--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="288">
   <si>
     <t>校区</t>
   </si>
@@ -546,6 +546,351 @@
   </si>
   <si>
     <t>B231604</t>
+  </si>
+  <si>
+    <t>通信与信息工程学院</t>
+  </si>
+  <si>
+    <t>TXXD09T0C</t>
+  </si>
+  <si>
+    <t>股票交易技术</t>
+  </si>
+  <si>
+    <t>朱成</t>
+  </si>
+  <si>
+    <t>B240303</t>
+  </si>
+  <si>
+    <t>B240418</t>
+  </si>
+  <si>
+    <t>B240518</t>
+  </si>
+  <si>
+    <t>B240905</t>
+  </si>
+  <si>
+    <t>B241001</t>
+  </si>
+  <si>
+    <t>B240226</t>
+  </si>
+  <si>
+    <t>B250108</t>
+  </si>
+  <si>
+    <t>B250110</t>
+  </si>
+  <si>
+    <t>B250120</t>
+  </si>
+  <si>
+    <t>B250121</t>
+  </si>
+  <si>
+    <t>B250123</t>
+  </si>
+  <si>
+    <t>B250209</t>
+  </si>
+  <si>
+    <t>B250213</t>
+  </si>
+  <si>
+    <t>B231804</t>
+  </si>
+  <si>
+    <t>B230903</t>
+  </si>
+  <si>
+    <t>B230901</t>
+  </si>
+  <si>
+    <t>B230425</t>
+  </si>
+  <si>
+    <t>B230404</t>
+  </si>
+  <si>
+    <t>B230400</t>
+  </si>
+  <si>
+    <t>B240217</t>
+  </si>
+  <si>
+    <t>B230123</t>
+  </si>
+  <si>
+    <t>B220416</t>
+  </si>
+  <si>
+    <t>B220219</t>
+  </si>
+  <si>
+    <t>B220218</t>
+  </si>
+  <si>
+    <t>B220211</t>
+  </si>
+  <si>
+    <t>B240207</t>
+  </si>
+  <si>
+    <t>B250404</t>
+  </si>
+  <si>
+    <t>B250313</t>
+  </si>
+  <si>
+    <t>B250315</t>
+  </si>
+  <si>
+    <t>B250316</t>
+  </si>
+  <si>
+    <t>B250400</t>
+  </si>
+  <si>
+    <t>B250402</t>
+  </si>
+  <si>
+    <t>B250309</t>
+  </si>
+  <si>
+    <t>B250413</t>
+  </si>
+  <si>
+    <t>B250417</t>
+  </si>
+  <si>
+    <t>B250511</t>
+  </si>
+  <si>
+    <t>B250515</t>
+  </si>
+  <si>
+    <t>B250611</t>
+  </si>
+  <si>
+    <t>B250612</t>
+  </si>
+  <si>
+    <t>B250217</t>
+  </si>
+  <si>
+    <t>B250911</t>
+  </si>
+  <si>
+    <t>B250301</t>
+  </si>
+  <si>
+    <t>B250307</t>
+  </si>
+  <si>
+    <t>B251602</t>
+  </si>
+  <si>
+    <t>B251208</t>
+  </si>
+  <si>
+    <t>B251201</t>
+  </si>
+  <si>
+    <t>B251101</t>
+  </si>
+  <si>
+    <t>B250914</t>
+  </si>
+  <si>
+    <t>B250222</t>
+  </si>
+  <si>
+    <t>B250908</t>
+  </si>
+  <si>
+    <t>B250903</t>
+  </si>
+  <si>
+    <t>B250802</t>
+  </si>
+  <si>
+    <t>TX116601S</t>
+  </si>
+  <si>
+    <t>无线通信原理(双语)</t>
+  </si>
+  <si>
+    <t>B230116</t>
+  </si>
+  <si>
+    <t>郭海燕/邹玉龙</t>
+  </si>
+  <si>
+    <t>教2－301</t>
+  </si>
+  <si>
+    <t>B230115</t>
+  </si>
+  <si>
+    <t>B230111</t>
+  </si>
+  <si>
+    <t>B220115</t>
+  </si>
+  <si>
+    <t>B220105</t>
+  </si>
+  <si>
+    <t>B230117</t>
+  </si>
+  <si>
+    <t>B230106</t>
+  </si>
+  <si>
+    <t>时艳玲/潘甦</t>
+  </si>
+  <si>
+    <t>B220102</t>
+  </si>
+  <si>
+    <t>B220104</t>
+  </si>
+  <si>
+    <t>B220110</t>
+  </si>
+  <si>
+    <t>B220111</t>
+  </si>
+  <si>
+    <t>B230110</t>
+  </si>
+  <si>
+    <t>B220114</t>
+  </si>
+  <si>
+    <t>王添顺</t>
+  </si>
+  <si>
+    <t>教2－300</t>
+  </si>
+  <si>
+    <t>B230113</t>
+  </si>
+  <si>
+    <t>B240103</t>
+  </si>
+  <si>
+    <t>B230109</t>
+  </si>
+  <si>
+    <t>B230112</t>
+  </si>
+  <si>
+    <t>B220101</t>
+  </si>
+  <si>
+    <t>B220113</t>
+  </si>
+  <si>
+    <t>B230107</t>
+  </si>
+  <si>
+    <t>吴叶增/杨海根</t>
+  </si>
+  <si>
+    <t>教2－302</t>
+  </si>
+  <si>
+    <t>B230108</t>
+  </si>
+  <si>
+    <t>宛汀/王鸿</t>
+  </si>
+  <si>
+    <t>胡晗/郑淦</t>
+  </si>
+  <si>
+    <t>教2－400</t>
+  </si>
+  <si>
+    <t>B230103</t>
+  </si>
+  <si>
+    <t>B220108</t>
+  </si>
+  <si>
+    <t>B230105</t>
+  </si>
+  <si>
+    <t>B230114</t>
+  </si>
+  <si>
+    <t>教2－401</t>
+  </si>
+  <si>
+    <t>B220107</t>
+  </si>
+  <si>
+    <t>王希瑶</t>
+  </si>
+  <si>
+    <t>B220109</t>
+  </si>
+  <si>
+    <t>B230104</t>
+  </si>
+  <si>
+    <t>B240108</t>
+  </si>
+  <si>
+    <t>教2－402</t>
+  </si>
+  <si>
+    <t>B230128</t>
+  </si>
+  <si>
+    <t>B230127</t>
+  </si>
+  <si>
+    <t>B230102</t>
+  </si>
+  <si>
+    <t>B230101</t>
+  </si>
+  <si>
+    <t>DG1114F4S</t>
+  </si>
+  <si>
+    <t>光电子基础实验</t>
+  </si>
+  <si>
+    <t>王始彦</t>
+  </si>
+  <si>
+    <t>沈淑婷</t>
+  </si>
+  <si>
+    <t>Q230101(TG)</t>
+  </si>
+  <si>
+    <t>庄艳玲</t>
+  </si>
+  <si>
+    <t>马晓波</t>
+  </si>
+  <si>
+    <t>张雪花</t>
+  </si>
+  <si>
+    <t>周纬</t>
+  </si>
+  <si>
+    <t>孙晓芸</t>
+  </si>
+  <si>
+    <t>杨朝雁</t>
   </si>
 </sst>
 </file>
@@ -913,7 +1258,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -930,36 +1275,6 @@
       </right>
       <top style="thin">
         <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="0"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -1090,7 +1405,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1102,34 +1417,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1214,7 +1529,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1234,12 +1549,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1770,7 +2079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4018,60 +4327,60 @@
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" s="7" t="s">
+      <c r="A78" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G78" s="7">
-        <v>1</v>
-      </c>
-      <c r="H78" s="7" t="s">
+      <c r="G78" s="6">
+        <v>1</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I78" s="7" t="s">
+      <c r="I78" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" s="8" t="s">
+      <c r="A79" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="6">
         <v>19</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="I79" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4108,28 +4417,28 @@
       <c r="A81" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="E81" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="F81" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G81" s="9">
-        <v>1</v>
-      </c>
-      <c r="H81" s="9" t="s">
+      <c r="G81" s="6">
+        <v>1</v>
+      </c>
+      <c r="H81" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I81" s="9" t="s">
+      <c r="I81" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4137,28 +4446,28 @@
       <c r="A82" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="E82" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="6">
         <v>2</v>
       </c>
-      <c r="H82" s="9" t="s">
+      <c r="H82" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I82" s="9" t="s">
+      <c r="I82" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4166,28 +4475,28 @@
       <c r="A83" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="C83" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="E83" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="F83" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="6">
         <v>3</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="H83" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I83" s="9" t="s">
+      <c r="I83" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4195,28 +4504,28 @@
       <c r="A84" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="E84" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="F84" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G84" s="9">
-        <v>1</v>
-      </c>
-      <c r="H84" s="9" t="s">
+      <c r="G84" s="6">
+        <v>1</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I84" s="9" t="s">
+      <c r="I84" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4224,28 +4533,28 @@
       <c r="A85" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="F85" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="6">
         <v>5</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="H85" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I85" s="9" t="s">
+      <c r="I85" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4253,28 +4562,28 @@
       <c r="A86" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="E86" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F86" s="9" t="s">
+      <c r="F86" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="6">
         <v>25</v>
       </c>
-      <c r="H86" s="9" t="s">
+      <c r="H86" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I86" s="9" t="s">
+      <c r="I86" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4282,28 +4591,28 @@
       <c r="A87" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D87" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="F87" s="9" t="s">
+      <c r="F87" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="6">
         <v>36</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="H87" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I87" s="9" t="s">
+      <c r="I87" s="6" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4311,28 +4620,28 @@
       <c r="A88" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F88" s="9" t="s">
+      <c r="F88" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="6">
         <v>34</v>
       </c>
-      <c r="H88" s="9" t="s">
+      <c r="H88" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I88" s="9" t="s">
+      <c r="I88" s="6" t="s">
         <v>161</v>
       </c>
     </row>
@@ -4340,28 +4649,28 @@
       <c r="A89" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="F89" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="6">
         <v>20</v>
       </c>
-      <c r="H89" s="9" t="s">
+      <c r="H89" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I89" s="9" t="s">
+      <c r="I89" s="6" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4369,28 +4678,28 @@
       <c r="A90" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="E90" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="F90" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="6">
         <v>20</v>
       </c>
-      <c r="H90" s="9" t="s">
+      <c r="H90" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I90" s="9" t="s">
+      <c r="I90" s="6" t="s">
         <v>161</v>
       </c>
     </row>
@@ -4508,6 +4817,3457 @@
       </c>
       <c r="I94" s="6" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G95" s="7">
+        <v>1</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G96" s="7">
+        <v>2</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G97" s="7">
+        <v>1</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G98" s="7">
+        <v>1</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G99" s="7">
+        <v>1</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G100" s="7">
+        <v>2</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G101" s="7">
+        <v>1</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G102" s="7">
+        <v>1</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G103" s="7">
+        <v>1</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G104" s="7">
+        <v>1</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G105" s="7">
+        <v>5</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G106" s="7">
+        <v>1</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G107" s="7">
+        <v>1</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G108" s="7">
+        <v>1</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G109" s="7">
+        <v>2</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G110" s="7">
+        <v>3</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G111" s="7">
+        <v>1</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G112" s="7">
+        <v>1</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G113" s="7">
+        <v>1</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G114" s="7">
+        <v>1</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G115" s="7">
+        <v>1</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G116" s="7">
+        <v>1</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G117" s="7">
+        <v>1</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G118" s="7">
+        <v>2</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G119" s="7">
+        <v>1</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G120" s="7">
+        <v>1</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G121" s="7">
+        <v>1</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G122" s="7">
+        <v>1</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G123" s="7">
+        <v>1</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G124" s="7">
+        <v>1</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G125" s="7">
+        <v>1</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G126" s="7">
+        <v>1</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G127" s="7">
+        <v>2</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G128" s="7">
+        <v>1</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G129" s="7">
+        <v>3</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G130" s="7">
+        <v>1</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G131" s="7">
+        <v>1</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G132" s="7">
+        <v>1</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G133" s="7">
+        <v>1</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G134" s="7">
+        <v>1</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G135" s="7">
+        <v>1</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I135" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G136" s="7">
+        <v>1</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G137" s="7">
+        <v>1</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G138" s="7">
+        <v>1</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G139" s="7">
+        <v>1</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I139" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G140" s="7">
+        <v>2</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G141" s="7">
+        <v>1</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I141" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G142" s="7">
+        <v>1</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G143" s="7">
+        <v>1</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G144" s="7">
+        <v>1</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G145" s="7">
+        <v>1</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G146" s="7">
+        <v>1</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G147" s="7">
+        <v>1</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G148" s="7">
+        <v>1</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G149" s="7">
+        <v>1</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G150" s="7">
+        <v>4</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G151" s="7">
+        <v>1</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G152" s="7">
+        <v>32</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G153" s="7">
+        <v>32</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G154" s="7">
+        <v>1</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G155" s="7">
+        <v>1</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G156" s="7">
+        <v>1</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G157" s="7">
+        <v>31</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G158" s="7">
+        <v>1</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G159" s="7">
+        <v>1</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G160" s="7">
+        <v>1</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G161" s="7">
+        <v>1</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G162" s="7">
+        <v>1</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G163" s="7">
+        <v>1</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G164" s="7">
+        <v>1</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G165" s="7">
+        <v>2</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G166" s="7">
+        <v>1</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G167" s="7">
+        <v>33</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I167" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G168" s="7">
+        <v>34</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G169" s="7">
+        <v>29</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G170" s="7">
+        <v>1</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G171" s="7">
+        <v>1</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G172" s="7">
+        <v>1</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I172" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G173" s="7">
+        <v>36</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G174" s="7">
+        <v>1</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I174" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G175" s="7">
+        <v>34</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I175" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G176" s="7">
+        <v>33</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I176" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G177" s="7">
+        <v>35</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I177" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G178" s="7">
+        <v>1</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G179" s="7">
+        <v>1</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G180" s="7">
+        <v>1</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G181" s="7">
+        <v>35</v>
+      </c>
+      <c r="H181" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G182" s="7">
+        <v>31</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G183" s="7">
+        <v>1</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G184" s="7">
+        <v>26</v>
+      </c>
+      <c r="H184" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G185" s="7">
+        <v>1</v>
+      </c>
+      <c r="H185" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G186" s="7">
+        <v>2</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G187" s="7">
+        <v>1</v>
+      </c>
+      <c r="H187" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G188" s="7">
+        <v>34</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G189" s="7">
+        <v>2</v>
+      </c>
+      <c r="H189" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G190" s="7">
+        <v>36</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G191" s="7">
+        <v>1</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G192" s="7">
+        <v>1</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G193" s="7">
+        <v>13</v>
+      </c>
+      <c r="H193" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G194" s="7">
+        <v>12</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G195" s="7">
+        <v>36</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G196" s="7">
+        <v>1</v>
+      </c>
+      <c r="H196" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G197" s="7">
+        <v>36</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G198" s="7">
+        <v>1</v>
+      </c>
+      <c r="H198" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G199" s="7">
+        <v>28</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G200" s="7">
+        <v>30</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G201" s="7">
+        <v>1</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G202" s="7">
+        <v>35</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G203" s="7">
+        <v>32</v>
+      </c>
+      <c r="H203" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G204" s="7">
+        <v>32</v>
+      </c>
+      <c r="H204" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G205" s="7">
+        <v>1</v>
+      </c>
+      <c r="H205" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G206" s="7">
+        <v>33</v>
+      </c>
+      <c r="H206" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G207" s="7">
+        <v>1</v>
+      </c>
+      <c r="H207" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G208" s="7">
+        <v>32</v>
+      </c>
+      <c r="H208" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G209" s="7">
+        <v>32</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G210" s="7">
+        <v>22</v>
+      </c>
+      <c r="H210" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G211" s="7">
+        <v>26</v>
+      </c>
+      <c r="H211" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G212" s="7">
+        <v>21</v>
+      </c>
+      <c r="H212" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G213" s="7">
+        <v>31</v>
+      </c>
+      <c r="H213" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="387">
   <si>
     <t>校区</t>
   </si>
@@ -996,6 +996,201 @@
   </si>
   <si>
     <t>B230503</t>
+  </si>
+  <si>
+    <t>GL1205GLS</t>
+  </si>
+  <si>
+    <t>公共关系</t>
+  </si>
+  <si>
+    <t>B231305(RL)</t>
+  </si>
+  <si>
+    <t>张耀珍/仲云云</t>
+  </si>
+  <si>
+    <t>第17周周2(2026-06-23) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>GL1519GLS</t>
+  </si>
+  <si>
+    <t>管理经济学</t>
+  </si>
+  <si>
+    <t>B251309</t>
+  </si>
+  <si>
+    <t>杨颖</t>
+  </si>
+  <si>
+    <t>第18周周1(2026-06-29) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>无2</t>
+  </si>
+  <si>
+    <t>B251308</t>
+  </si>
+  <si>
+    <t>GL1712GLS</t>
+  </si>
+  <si>
+    <t>商务智能</t>
+  </si>
+  <si>
+    <t>B231309</t>
+  </si>
+  <si>
+    <t>朱恒民</t>
+  </si>
+  <si>
+    <t>第17周周3(2026-06-24) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>无1</t>
+  </si>
+  <si>
+    <t>B231307</t>
+  </si>
+  <si>
+    <t>B231308</t>
+  </si>
+  <si>
+    <t>B231301(GG)</t>
+  </si>
+  <si>
+    <t>王伟</t>
+  </si>
+  <si>
+    <t>无3</t>
+  </si>
+  <si>
+    <t>GL1712GLC</t>
+  </si>
+  <si>
+    <t>魏建香</t>
+  </si>
+  <si>
+    <t>B231300</t>
+  </si>
+  <si>
+    <t>刘凯</t>
+  </si>
+  <si>
+    <t>沈超</t>
+  </si>
+  <si>
+    <t>B231303(CW)</t>
+  </si>
+  <si>
+    <t>B231302(CW)</t>
+  </si>
+  <si>
+    <t>GL4931HWS</t>
+  </si>
+  <si>
+    <t>F231301</t>
+  </si>
+  <si>
+    <t>孙建敏</t>
+  </si>
+  <si>
+    <t>第16周周7(2026-06-21) 18:30-20:20</t>
+  </si>
+  <si>
+    <t>F221301</t>
+  </si>
+  <si>
+    <t>F230101</t>
+  </si>
+  <si>
+    <t>F231302</t>
+  </si>
+  <si>
+    <t>GL4920HWC</t>
+  </si>
+  <si>
+    <t>运营管理</t>
+  </si>
+  <si>
+    <t>F241202</t>
+  </si>
+  <si>
+    <t>彭英</t>
+  </si>
+  <si>
+    <t>第16周周4(2026-06-18) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>F241201</t>
+  </si>
+  <si>
+    <t>GL1211GLC</t>
+  </si>
+  <si>
+    <t>电信运营管理</t>
+  </si>
+  <si>
+    <t>付金朋</t>
+  </si>
+  <si>
+    <t>第16周周3(2026-06-17) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>GL1212GLC</t>
+  </si>
+  <si>
+    <t>姜丽宁</t>
+  </si>
+  <si>
+    <t>B221310</t>
+  </si>
+  <si>
+    <t>B221311</t>
+  </si>
+  <si>
+    <t>GL1203G2S</t>
+  </si>
+  <si>
+    <t>市场营销</t>
+  </si>
+  <si>
+    <t>闻超群</t>
+  </si>
+  <si>
+    <t>第15周周3(2026-06-10) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>B241209</t>
+  </si>
+  <si>
+    <t>唐娟</t>
+  </si>
+  <si>
+    <t>GL1110G2S</t>
+  </si>
+  <si>
+    <t>B241202</t>
+  </si>
+  <si>
+    <t>石盛林</t>
+  </si>
+  <si>
+    <t>第14周周3(2026-06-03) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>B241201</t>
+  </si>
+  <si>
+    <t>GL1109G2S</t>
+  </si>
+  <si>
+    <t>质量管理</t>
+  </si>
+  <si>
+    <t>第12周周5(2026-05-22) 18:30-20:20</t>
   </si>
 </sst>
 </file>
@@ -2184,7 +2379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I242"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -8814,28 +9009,28 @@
       <c r="A229" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C229" s="7" t="s">
+      <c r="C229" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D229" s="7" t="s">
+      <c r="D229" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E229" s="7" t="s">
+      <c r="E229" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F229" s="7" t="s">
+      <c r="F229" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G229" s="7">
-        <v>1</v>
-      </c>
-      <c r="H229" s="7" t="s">
+      <c r="G229" s="6">
+        <v>1</v>
+      </c>
+      <c r="H229" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I229" s="7" t="s">
+      <c r="I229" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8843,28 +9038,28 @@
       <c r="A230" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C230" s="7" t="s">
+      <c r="C230" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D230" s="7" t="s">
+      <c r="D230" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E230" s="7" t="s">
+      <c r="E230" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F230" s="7" t="s">
+      <c r="F230" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G230" s="7">
-        <v>1</v>
-      </c>
-      <c r="H230" s="7" t="s">
+      <c r="G230" s="6">
+        <v>1</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I230" s="7" t="s">
+      <c r="I230" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8872,28 +9067,28 @@
       <c r="A231" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C231" s="7" t="s">
+      <c r="C231" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D231" s="7" t="s">
+      <c r="D231" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E231" s="7" t="s">
+      <c r="E231" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F231" s="7" t="s">
+      <c r="F231" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G231" s="7">
-        <v>1</v>
-      </c>
-      <c r="H231" s="7" t="s">
+      <c r="G231" s="6">
+        <v>1</v>
+      </c>
+      <c r="H231" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I231" s="7" t="s">
+      <c r="I231" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8901,28 +9096,28 @@
       <c r="A232" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C232" s="7" t="s">
+      <c r="C232" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D232" s="7" t="s">
+      <c r="D232" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E232" s="7" t="s">
+      <c r="E232" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="F232" s="7" t="s">
+      <c r="F232" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G232" s="7">
+      <c r="G232" s="6">
         <v>2</v>
       </c>
-      <c r="H232" s="7" t="s">
+      <c r="H232" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I232" s="7" t="s">
+      <c r="I232" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8930,28 +9125,28 @@
       <c r="A233" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C233" s="7" t="s">
+      <c r="C233" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D233" s="7" t="s">
+      <c r="D233" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E233" s="7" t="s">
+      <c r="E233" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F233" s="7" t="s">
+      <c r="F233" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G233" s="7">
-        <v>1</v>
-      </c>
-      <c r="H233" s="7" t="s">
+      <c r="G233" s="6">
+        <v>1</v>
+      </c>
+      <c r="H233" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I233" s="7" t="s">
+      <c r="I233" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8959,28 +9154,28 @@
       <c r="A234" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C234" s="7" t="s">
+      <c r="C234" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D234" s="7" t="s">
+      <c r="D234" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E234" s="7" t="s">
+      <c r="E234" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F234" s="7" t="s">
+      <c r="F234" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G234" s="7">
-        <v>1</v>
-      </c>
-      <c r="H234" s="7" t="s">
+      <c r="G234" s="6">
+        <v>1</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I234" s="7" t="s">
+      <c r="I234" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -8988,28 +9183,28 @@
       <c r="A235" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C235" s="7" t="s">
+      <c r="C235" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D235" s="7" t="s">
+      <c r="D235" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E235" s="7" t="s">
+      <c r="E235" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F235" s="7" t="s">
+      <c r="F235" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G235" s="7">
+      <c r="G235" s="6">
         <v>4</v>
       </c>
-      <c r="H235" s="7" t="s">
+      <c r="H235" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I235" s="7" t="s">
+      <c r="I235" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9017,28 +9212,28 @@
       <c r="A236" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C236" s="7" t="s">
+      <c r="C236" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D236" s="7" t="s">
+      <c r="D236" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E236" s="7" t="s">
+      <c r="E236" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F236" s="7" t="s">
+      <c r="F236" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G236" s="7">
-        <v>1</v>
-      </c>
-      <c r="H236" s="7" t="s">
+      <c r="G236" s="6">
+        <v>1</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I236" s="7" t="s">
+      <c r="I236" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9046,28 +9241,28 @@
       <c r="A237" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C237" s="7" t="s">
+      <c r="C237" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D237" s="7" t="s">
+      <c r="D237" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E237" s="7" t="s">
+      <c r="E237" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F237" s="7" t="s">
+      <c r="F237" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G237" s="7">
+      <c r="G237" s="6">
         <v>3</v>
       </c>
-      <c r="H237" s="7" t="s">
+      <c r="H237" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I237" s="7" t="s">
+      <c r="I237" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9075,28 +9270,28 @@
       <c r="A238" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C238" s="7" t="s">
+      <c r="C238" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D238" s="7" t="s">
+      <c r="D238" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E238" s="7" t="s">
+      <c r="E238" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F238" s="7" t="s">
+      <c r="F238" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G238" s="7">
-        <v>1</v>
-      </c>
-      <c r="H238" s="7" t="s">
+      <c r="G238" s="6">
+        <v>1</v>
+      </c>
+      <c r="H238" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I238" s="7" t="s">
+      <c r="I238" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9104,28 +9299,28 @@
       <c r="A239" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C239" s="7" t="s">
+      <c r="C239" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D239" s="7" t="s">
+      <c r="D239" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E239" s="7" t="s">
+      <c r="E239" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F239" s="7" t="s">
+      <c r="F239" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G239" s="7">
-        <v>1</v>
-      </c>
-      <c r="H239" s="7" t="s">
+      <c r="G239" s="6">
+        <v>1</v>
+      </c>
+      <c r="H239" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I239" s="7" t="s">
+      <c r="I239" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9133,28 +9328,28 @@
       <c r="A240" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B240" s="7" t="s">
+      <c r="B240" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C240" s="7" t="s">
+      <c r="C240" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D240" s="7" t="s">
+      <c r="D240" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E240" s="7" t="s">
+      <c r="E240" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F240" s="7" t="s">
+      <c r="F240" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G240" s="7">
+      <c r="G240" s="6">
         <v>2</v>
       </c>
-      <c r="H240" s="7" t="s">
+      <c r="H240" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I240" s="7" t="s">
+      <c r="I240" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9162,28 +9357,28 @@
       <c r="A241" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C241" s="7" t="s">
+      <c r="C241" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D241" s="7" t="s">
+      <c r="D241" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E241" s="7" t="s">
+      <c r="E241" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="F241" s="7" t="s">
+      <c r="F241" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G241" s="7">
+      <c r="G241" s="6">
         <v>2</v>
       </c>
-      <c r="H241" s="7" t="s">
+      <c r="H241" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I241" s="7" t="s">
+      <c r="I241" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -9191,35 +9386,1134 @@
       <c r="A242" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B242" s="7" t="s">
+      <c r="B242" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C242" s="7" t="s">
+      <c r="C242" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D242" s="7" t="s">
+      <c r="D242" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E242" s="7" t="s">
+      <c r="E242" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="F242" s="7" t="s">
+      <c r="F242" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G242" s="7">
-        <v>1</v>
-      </c>
-      <c r="H242" s="7" t="s">
+      <c r="G242" s="6">
+        <v>1</v>
+      </c>
+      <c r="H242" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="I242" s="7" t="s">
+      <c r="I242" s="6" t="s">
         <v>309</v>
       </c>
     </row>
+    <row r="243" spans="1:9">
+      <c r="A243" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E243" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F243" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G243" s="7">
+        <v>18</v>
+      </c>
+      <c r="H243" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="I243" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E244" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="G244" s="7">
+        <v>30</v>
+      </c>
+      <c r="H244" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="I244" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="G245" s="7">
+        <v>28</v>
+      </c>
+      <c r="H245" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="I245" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G246" s="7">
+        <v>23</v>
+      </c>
+      <c r="H246" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I246" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B247" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E247" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G247" s="7">
+        <v>25</v>
+      </c>
+      <c r="H247" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I247" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E248" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G248" s="7">
+        <v>26</v>
+      </c>
+      <c r="H248" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D249" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E249" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G249" s="7">
+        <v>21</v>
+      </c>
+      <c r="H249" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="G250" s="7">
+        <v>28</v>
+      </c>
+      <c r="H250" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I250" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E251" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G251" s="7">
+        <v>26</v>
+      </c>
+      <c r="H251" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I251" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B252" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C252" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E252" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G252" s="7">
+        <v>10</v>
+      </c>
+      <c r="H252" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C253" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E253" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G253" s="7">
+        <v>19</v>
+      </c>
+      <c r="H253" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E254" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G254" s="7">
+        <v>21</v>
+      </c>
+      <c r="H254" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C255" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D255" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E255" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G255" s="7">
+        <v>26</v>
+      </c>
+      <c r="H255" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G256" s="7">
+        <v>1</v>
+      </c>
+      <c r="H256" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D257" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E257" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G257" s="7">
+        <v>1</v>
+      </c>
+      <c r="H257" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I257" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D258" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E258" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G258" s="7">
+        <v>22</v>
+      </c>
+      <c r="H258" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D259" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E259" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G259" s="7">
+        <v>25</v>
+      </c>
+      <c r="H259" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E260" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G260" s="7">
+        <v>23</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B261" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D261" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E261" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G261" s="7">
+        <v>1</v>
+      </c>
+      <c r="H261" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I261" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G262" s="7">
+        <v>19</v>
+      </c>
+      <c r="H262" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B263" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F263" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G263" s="7">
+        <v>18</v>
+      </c>
+      <c r="H263" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I263" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B264" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E264" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F264" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G264" s="7">
+        <v>2</v>
+      </c>
+      <c r="H264" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B265" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D265" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E265" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G265" s="7">
+        <v>5</v>
+      </c>
+      <c r="H265" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I265" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B266" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E266" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G266" s="7">
+        <v>2</v>
+      </c>
+      <c r="H266" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G267" s="7">
+        <v>10</v>
+      </c>
+      <c r="H267" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I267" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B268" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C268" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E268" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G268" s="7">
+        <v>21</v>
+      </c>
+      <c r="H268" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E269" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G269" s="7">
+        <v>1</v>
+      </c>
+      <c r="H269" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I269" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F270" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G270" s="7">
+        <v>2</v>
+      </c>
+      <c r="H270" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E271" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G271" s="7">
+        <v>12</v>
+      </c>
+      <c r="H271" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I271" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B272" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E272" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G272" s="7">
+        <v>1</v>
+      </c>
+      <c r="H272" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F273" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G273" s="7">
+        <v>2</v>
+      </c>
+      <c r="H273" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I273" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F274" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G274" s="7">
+        <v>19</v>
+      </c>
+      <c r="H274" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I274" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F275" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G275" s="7">
+        <v>4</v>
+      </c>
+      <c r="H275" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I275" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E276" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F276" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G276" s="7">
+        <v>1</v>
+      </c>
+      <c r="H276" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I276" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E277" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G277" s="7">
+        <v>28</v>
+      </c>
+      <c r="H277" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I277" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E278" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G278" s="7">
+        <v>24</v>
+      </c>
+      <c r="H278" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E279" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G279" s="7">
+        <v>24</v>
+      </c>
+      <c r="H279" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="I279" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G280" s="7">
+        <v>21</v>
+      </c>
+      <c r="H280" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I228" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4129" uniqueCount="503">
   <si>
     <t>校区</t>
   </si>
@@ -1191,6 +1191,354 @@
   </si>
   <si>
     <t>第12周周5(2026-05-22) 18:30-20:20</t>
+  </si>
+  <si>
+    <t>TX3186PIS</t>
+  </si>
+  <si>
+    <t>宽带无线通信技术</t>
+  </si>
+  <si>
+    <t>P220001</t>
+  </si>
+  <si>
+    <t>P220002</t>
+  </si>
+  <si>
+    <t>P220003</t>
+  </si>
+  <si>
+    <t>P220004</t>
+  </si>
+  <si>
+    <t>P230003</t>
+  </si>
+  <si>
+    <t>TX134103S</t>
+  </si>
+  <si>
+    <t>机器学习</t>
+  </si>
+  <si>
+    <t>B240426</t>
+  </si>
+  <si>
+    <t>张行/闫静杰</t>
+  </si>
+  <si>
+    <t>第17周周3(2026-06-24) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>教2－204</t>
+  </si>
+  <si>
+    <t>B240130</t>
+  </si>
+  <si>
+    <t>B240129</t>
+  </si>
+  <si>
+    <t>B240427</t>
+  </si>
+  <si>
+    <t>TX126402S</t>
+  </si>
+  <si>
+    <t>密码学与人工智能安全</t>
+  </si>
+  <si>
+    <t>B220118</t>
+  </si>
+  <si>
+    <t>B230118</t>
+  </si>
+  <si>
+    <t>B230119</t>
+  </si>
+  <si>
+    <t>B230120</t>
+  </si>
+  <si>
+    <t>B230121</t>
+  </si>
+  <si>
+    <t>B230122</t>
+  </si>
+  <si>
+    <t>B230124</t>
+  </si>
+  <si>
+    <t>B230125</t>
+  </si>
+  <si>
+    <t>B230126</t>
+  </si>
+  <si>
+    <t>TX126102C</t>
+  </si>
+  <si>
+    <t>Python语言编程与工程实践</t>
+  </si>
+  <si>
+    <t>B220123</t>
+  </si>
+  <si>
+    <t>黄波</t>
+  </si>
+  <si>
+    <t>第13周周6(2026-05-30) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>教3－102</t>
+  </si>
+  <si>
+    <t>B220125</t>
+  </si>
+  <si>
+    <t>教3－201</t>
+  </si>
+  <si>
+    <t>吴聪/孙宁</t>
+  </si>
+  <si>
+    <t>教3－204</t>
+  </si>
+  <si>
+    <t>TX125102S</t>
+  </si>
+  <si>
+    <t>算法与数据结构</t>
+  </si>
+  <si>
+    <t>B240115</t>
+  </si>
+  <si>
+    <t>程铭</t>
+  </si>
+  <si>
+    <t>第17周周5(2026-06-26) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>欧阳键</t>
+  </si>
+  <si>
+    <t>B240114</t>
+  </si>
+  <si>
+    <t>B240106</t>
+  </si>
+  <si>
+    <t>B240113</t>
+  </si>
+  <si>
+    <t>B240110</t>
+  </si>
+  <si>
+    <t>B240109</t>
+  </si>
+  <si>
+    <t>B240107</t>
+  </si>
+  <si>
+    <t>B240105</t>
+  </si>
+  <si>
+    <t>B240112</t>
+  </si>
+  <si>
+    <t>教2－403</t>
+  </si>
+  <si>
+    <t>B240111</t>
+  </si>
+  <si>
+    <t>B240101</t>
+  </si>
+  <si>
+    <t>B240104</t>
+  </si>
+  <si>
+    <t>B240117</t>
+  </si>
+  <si>
+    <t>B240116</t>
+  </si>
+  <si>
+    <t>B240118</t>
+  </si>
+  <si>
+    <t>B240102</t>
+  </si>
+  <si>
+    <t>TX116801C</t>
+  </si>
+  <si>
+    <t>新型网络技术基础</t>
+  </si>
+  <si>
+    <t>吴斌</t>
+  </si>
+  <si>
+    <t>第16周周6(2026-06-20) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>孙晓玲</t>
+  </si>
+  <si>
+    <t>Q230102(TG)</t>
+  </si>
+  <si>
+    <t>TX116701C</t>
+  </si>
+  <si>
+    <t>Q230103(JK)</t>
+  </si>
+  <si>
+    <t>王昕</t>
+  </si>
+  <si>
+    <t>杨丽花/徐鼎</t>
+  </si>
+  <si>
+    <t>王视环</t>
+  </si>
+  <si>
+    <t>Q230101(JK)</t>
+  </si>
+  <si>
+    <t>王视环/朱琦</t>
+  </si>
+  <si>
+    <t>B220112</t>
+  </si>
+  <si>
+    <t>TX116202S</t>
+  </si>
+  <si>
+    <t>通信网络技术（双语）</t>
+  </si>
+  <si>
+    <t>江凌云/杨龙祥</t>
+  </si>
+  <si>
+    <t>第17周周6(2026-06-27) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>B220124</t>
+  </si>
+  <si>
+    <t>B220120</t>
+  </si>
+  <si>
+    <t>B220119</t>
+  </si>
+  <si>
+    <t>王珺/郭永安</t>
+  </si>
+  <si>
+    <t>B220117</t>
+  </si>
+  <si>
+    <t>B220122</t>
+  </si>
+  <si>
+    <t>B200124</t>
+  </si>
+  <si>
+    <t>教2－103</t>
+  </si>
+  <si>
+    <t>B220121</t>
+  </si>
+  <si>
+    <t>TX105201S</t>
+  </si>
+  <si>
+    <t>数字信号处理B</t>
+  </si>
+  <si>
+    <t>朱艳</t>
+  </si>
+  <si>
+    <t>徐挺挺</t>
+  </si>
+  <si>
+    <t>李斌/张玲华</t>
+  </si>
+  <si>
+    <t>叶蕾/王婕</t>
+  </si>
+  <si>
+    <t>梁涓</t>
+  </si>
+  <si>
+    <t>TX109001S</t>
+  </si>
+  <si>
+    <t>数字信号处理（双语）</t>
+  </si>
+  <si>
+    <t>Q240101</t>
+  </si>
+  <si>
+    <t>徐欣</t>
+  </si>
+  <si>
+    <t>Q240102</t>
+  </si>
+  <si>
+    <t>Q240103</t>
+  </si>
+  <si>
+    <t>Q240104</t>
+  </si>
+  <si>
+    <t>Q240105</t>
+  </si>
+  <si>
+    <t>王颖翠/邵曦</t>
+  </si>
+  <si>
+    <t>TX104001S</t>
+  </si>
+  <si>
+    <t>通信原理（混合式）</t>
+  </si>
+  <si>
+    <t>何雪云</t>
+  </si>
+  <si>
+    <t>第16周周1(2026-06-15) 18:30-20:20</t>
+  </si>
+  <si>
+    <t>教3－408</t>
+  </si>
+  <si>
+    <t>TX104002S</t>
+  </si>
+  <si>
+    <t>TX104003S</t>
+  </si>
+  <si>
+    <t>经济学院</t>
+  </si>
+  <si>
+    <t>JJ116901S</t>
+  </si>
+  <si>
+    <t>经济思想史</t>
+  </si>
+  <si>
+    <t>B231401(JJ)</t>
+  </si>
+  <si>
+    <t>牟立邦</t>
+  </si>
+  <si>
+    <t>第12周周4(2026-05-21) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>教4－406</t>
   </si>
 </sst>
 </file>
@@ -2379,7 +2727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I280"/>
+  <dimension ref="A1:I516"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -9415,28 +9763,28 @@
       <c r="A243" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B243" s="7" t="s">
+      <c r="B243" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C243" s="7" t="s">
+      <c r="C243" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D243" s="7" t="s">
+      <c r="D243" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E243" s="7" t="s">
+      <c r="E243" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F243" s="7" t="s">
+      <c r="F243" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="G243" s="7">
+      <c r="G243" s="6">
         <v>18</v>
       </c>
-      <c r="H243" s="7" t="s">
+      <c r="H243" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="I243" s="7" t="s">
+      <c r="I243" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -9444,28 +9792,28 @@
       <c r="A244" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B244" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C244" s="7" t="s">
+      <c r="C244" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="D244" s="7" t="s">
+      <c r="D244" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E244" s="7" t="s">
+      <c r="E244" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="F244" s="7" t="s">
+      <c r="F244" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G244" s="7">
+      <c r="G244" s="6">
         <v>30</v>
       </c>
-      <c r="H244" s="7" t="s">
+      <c r="H244" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="I244" s="7" t="s">
+      <c r="I244" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -9473,28 +9821,28 @@
       <c r="A245" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C245" s="7" t="s">
+      <c r="C245" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="D245" s="7" t="s">
+      <c r="D245" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E245" s="7" t="s">
+      <c r="E245" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="F245" s="7" t="s">
+      <c r="F245" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G245" s="7">
+      <c r="G245" s="6">
         <v>28</v>
       </c>
-      <c r="H245" s="7" t="s">
+      <c r="H245" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="I245" s="7" t="s">
+      <c r="I245" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -9502,28 +9850,28 @@
       <c r="A246" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="B246" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C246" s="7" t="s">
+      <c r="C246" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D246" s="7" t="s">
+      <c r="D246" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E246" s="7" t="s">
+      <c r="E246" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F246" s="7" t="s">
+      <c r="F246" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G246" s="7">
+      <c r="G246" s="6">
         <v>23</v>
       </c>
-      <c r="H246" s="7" t="s">
+      <c r="H246" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I246" s="7" t="s">
+      <c r="I246" s="6" t="s">
         <v>339</v>
       </c>
     </row>
@@ -9531,28 +9879,28 @@
       <c r="A247" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B247" s="7" t="s">
+      <c r="B247" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C247" s="7" t="s">
+      <c r="C247" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D247" s="7" t="s">
+      <c r="D247" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E247" s="7" t="s">
+      <c r="E247" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F247" s="7" t="s">
+      <c r="F247" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G247" s="7">
+      <c r="G247" s="6">
         <v>25</v>
       </c>
-      <c r="H247" s="7" t="s">
+      <c r="H247" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I247" s="7" t="s">
+      <c r="I247" s="6" t="s">
         <v>339</v>
       </c>
     </row>
@@ -9560,28 +9908,28 @@
       <c r="A248" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B248" s="7" t="s">
+      <c r="B248" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C248" s="7" t="s">
+      <c r="C248" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D248" s="7" t="s">
+      <c r="D248" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E248" s="7" t="s">
+      <c r="E248" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F248" s="7" t="s">
+      <c r="F248" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G248" s="7">
+      <c r="G248" s="6">
         <v>26</v>
       </c>
-      <c r="H248" s="7" t="s">
+      <c r="H248" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I248" s="7" t="s">
+      <c r="I248" s="6" t="s">
         <v>339</v>
       </c>
     </row>
@@ -9589,28 +9937,28 @@
       <c r="A249" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B249" s="7" t="s">
+      <c r="B249" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C249" s="7" t="s">
+      <c r="C249" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D249" s="7" t="s">
+      <c r="D249" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E249" s="7" t="s">
+      <c r="E249" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F249" s="7" t="s">
+      <c r="F249" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G249" s="7">
+      <c r="G249" s="6">
         <v>21</v>
       </c>
-      <c r="H249" s="7" t="s">
+      <c r="H249" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I249" s="7" t="s">
+      <c r="I249" s="6" t="s">
         <v>344</v>
       </c>
     </row>
@@ -9618,28 +9966,28 @@
       <c r="A250" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B250" s="7" t="s">
+      <c r="B250" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C250" s="7" t="s">
+      <c r="C250" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="D250" s="7" t="s">
+      <c r="D250" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E250" s="7" t="s">
+      <c r="E250" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F250" s="7" t="s">
+      <c r="F250" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G250" s="7">
+      <c r="G250" s="6">
         <v>28</v>
       </c>
-      <c r="H250" s="7" t="s">
+      <c r="H250" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I250" s="7" t="s">
+      <c r="I250" s="6" t="s">
         <v>344</v>
       </c>
     </row>
@@ -9647,28 +9995,28 @@
       <c r="A251" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B251" s="7" t="s">
+      <c r="B251" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C251" s="7" t="s">
+      <c r="C251" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D251" s="7" t="s">
+      <c r="D251" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E251" s="7" t="s">
+      <c r="E251" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="F251" s="7" t="s">
+      <c r="F251" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="G251" s="7">
+      <c r="G251" s="6">
         <v>26</v>
       </c>
-      <c r="H251" s="7" t="s">
+      <c r="H251" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I251" s="7" t="s">
+      <c r="I251" s="6" t="s">
         <v>344</v>
       </c>
     </row>
@@ -9676,28 +10024,28 @@
       <c r="A252" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B252" s="7" t="s">
+      <c r="B252" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C252" s="7" t="s">
+      <c r="C252" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="D252" s="7" t="s">
+      <c r="D252" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E252" s="7" t="s">
+      <c r="E252" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F252" s="7" t="s">
+      <c r="F252" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G252" s="7">
+      <c r="G252" s="6">
         <v>10</v>
       </c>
-      <c r="H252" s="7" t="s">
+      <c r="H252" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I252" s="7" t="s">
+      <c r="I252" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -9705,28 +10053,28 @@
       <c r="A253" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C253" s="7" t="s">
+      <c r="C253" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="D253" s="7" t="s">
+      <c r="D253" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E253" s="7" t="s">
+      <c r="E253" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F253" s="7" t="s">
+      <c r="F253" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G253" s="7">
+      <c r="G253" s="6">
         <v>19</v>
       </c>
-      <c r="H253" s="7" t="s">
+      <c r="H253" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I253" s="7" t="s">
+      <c r="I253" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -9734,28 +10082,28 @@
       <c r="A254" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B254" s="7" t="s">
+      <c r="B254" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C254" s="7" t="s">
+      <c r="C254" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="D254" s="7" t="s">
+      <c r="D254" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E254" s="7" t="s">
+      <c r="E254" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="F254" s="7" t="s">
+      <c r="F254" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G254" s="7">
+      <c r="G254" s="6">
         <v>21</v>
       </c>
-      <c r="H254" s="7" t="s">
+      <c r="H254" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I254" s="7" t="s">
+      <c r="I254" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -9763,28 +10111,28 @@
       <c r="A255" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B255" s="7" t="s">
+      <c r="B255" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C255" s="7" t="s">
+      <c r="C255" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D255" s="7" t="s">
+      <c r="D255" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E255" s="7" t="s">
+      <c r="E255" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F255" s="7" t="s">
+      <c r="F255" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G255" s="7">
+      <c r="G255" s="6">
         <v>26</v>
       </c>
-      <c r="H255" s="7" t="s">
+      <c r="H255" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="I255" s="7" t="s">
+      <c r="I255" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9792,28 +10140,28 @@
       <c r="A256" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B256" s="7" t="s">
+      <c r="B256" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C256" s="7" t="s">
+      <c r="C256" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D256" s="7" t="s">
+      <c r="D256" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E256" s="7" t="s">
+      <c r="E256" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F256" s="7" t="s">
+      <c r="F256" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G256" s="7">
-        <v>1</v>
-      </c>
-      <c r="H256" s="7" t="s">
+      <c r="G256" s="6">
+        <v>1</v>
+      </c>
+      <c r="H256" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="I256" s="7" t="s">
+      <c r="I256" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9821,28 +10169,28 @@
       <c r="A257" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B257" s="7" t="s">
+      <c r="B257" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C257" s="7" t="s">
+      <c r="C257" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D257" s="7" t="s">
+      <c r="D257" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E257" s="7" t="s">
+      <c r="E257" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F257" s="7" t="s">
+      <c r="F257" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G257" s="7">
-        <v>1</v>
-      </c>
-      <c r="H257" s="7" t="s">
+      <c r="G257" s="6">
+        <v>1</v>
+      </c>
+      <c r="H257" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="I257" s="7" t="s">
+      <c r="I257" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9850,28 +10198,28 @@
       <c r="A258" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B258" s="7" t="s">
+      <c r="B258" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C258" s="7" t="s">
+      <c r="C258" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D258" s="7" t="s">
+      <c r="D258" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E258" s="7" t="s">
+      <c r="E258" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="F258" s="7" t="s">
+      <c r="F258" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G258" s="7">
+      <c r="G258" s="6">
         <v>22</v>
       </c>
-      <c r="H258" s="7" t="s">
+      <c r="H258" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="I258" s="7" t="s">
+      <c r="I258" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9879,28 +10227,28 @@
       <c r="A259" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B259" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C259" s="7" t="s">
+      <c r="C259" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="D259" s="7" t="s">
+      <c r="D259" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E259" s="7" t="s">
+      <c r="E259" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="F259" s="7" t="s">
+      <c r="F259" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G259" s="7">
+      <c r="G259" s="6">
         <v>25</v>
       </c>
-      <c r="H259" s="7" t="s">
+      <c r="H259" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="I259" s="7" t="s">
+      <c r="I259" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9908,28 +10256,28 @@
       <c r="A260" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B260" s="7" t="s">
+      <c r="B260" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C260" s="7" t="s">
+      <c r="C260" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="D260" s="7" t="s">
+      <c r="D260" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E260" s="7" t="s">
+      <c r="E260" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="F260" s="7" t="s">
+      <c r="F260" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G260" s="7">
+      <c r="G260" s="6">
         <v>23</v>
       </c>
-      <c r="H260" s="7" t="s">
+      <c r="H260" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="I260" s="7" t="s">
+      <c r="I260" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9937,28 +10285,28 @@
       <c r="A261" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B261" s="7" t="s">
+      <c r="B261" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C261" s="7" t="s">
+      <c r="C261" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D261" s="7" t="s">
+      <c r="D261" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E261" s="7" t="s">
+      <c r="E261" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F261" s="7" t="s">
+      <c r="F261" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G261" s="7">
-        <v>1</v>
-      </c>
-      <c r="H261" s="7" t="s">
+      <c r="G261" s="6">
+        <v>1</v>
+      </c>
+      <c r="H261" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I261" s="7" t="s">
+      <c r="I261" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -9966,28 +10314,28 @@
       <c r="A262" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B262" s="7" t="s">
+      <c r="B262" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C262" s="7" t="s">
+      <c r="C262" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D262" s="7" t="s">
+      <c r="D262" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E262" s="7" t="s">
+      <c r="E262" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F262" s="7" t="s">
+      <c r="F262" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G262" s="7">
+      <c r="G262" s="6">
         <v>19</v>
       </c>
-      <c r="H262" s="7" t="s">
+      <c r="H262" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I262" s="7" t="s">
+      <c r="I262" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -9995,28 +10343,28 @@
       <c r="A263" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B263" s="7" t="s">
+      <c r="B263" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C263" s="7" t="s">
+      <c r="C263" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D263" s="7" t="s">
+      <c r="D263" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E263" s="7" t="s">
+      <c r="E263" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F263" s="7" t="s">
+      <c r="F263" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G263" s="7">
+      <c r="G263" s="6">
         <v>18</v>
       </c>
-      <c r="H263" s="7" t="s">
+      <c r="H263" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I263" s="7" t="s">
+      <c r="I263" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10024,28 +10372,28 @@
       <c r="A264" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B264" s="7" t="s">
+      <c r="B264" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C264" s="7" t="s">
+      <c r="C264" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D264" s="7" t="s">
+      <c r="D264" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E264" s="7" t="s">
+      <c r="E264" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F264" s="7" t="s">
+      <c r="F264" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G264" s="7">
+      <c r="G264" s="6">
         <v>2</v>
       </c>
-      <c r="H264" s="7" t="s">
+      <c r="H264" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I264" s="7" t="s">
+      <c r="I264" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10053,28 +10401,28 @@
       <c r="A265" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B265" s="7" t="s">
+      <c r="B265" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C265" s="7" t="s">
+      <c r="C265" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D265" s="7" t="s">
+      <c r="D265" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E265" s="7" t="s">
+      <c r="E265" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="F265" s="7" t="s">
+      <c r="F265" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G265" s="7">
+      <c r="G265" s="6">
         <v>5</v>
       </c>
-      <c r="H265" s="7" t="s">
+      <c r="H265" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I265" s="7" t="s">
+      <c r="I265" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10082,28 +10430,28 @@
       <c r="A266" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B266" s="7" t="s">
+      <c r="B266" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C266" s="7" t="s">
+      <c r="C266" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D266" s="7" t="s">
+      <c r="D266" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E266" s="7" t="s">
+      <c r="E266" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="F266" s="7" t="s">
+      <c r="F266" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G266" s="7">
+      <c r="G266" s="6">
         <v>2</v>
       </c>
-      <c r="H266" s="7" t="s">
+      <c r="H266" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I266" s="7" t="s">
+      <c r="I266" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10111,28 +10459,28 @@
       <c r="A267" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B267" s="7" t="s">
+      <c r="B267" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C267" s="7" t="s">
+      <c r="C267" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D267" s="7" t="s">
+      <c r="D267" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E267" s="7" t="s">
+      <c r="E267" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F267" s="7" t="s">
+      <c r="F267" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G267" s="7">
+      <c r="G267" s="6">
         <v>10</v>
       </c>
-      <c r="H267" s="7" t="s">
+      <c r="H267" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I267" s="7" t="s">
+      <c r="I267" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10140,28 +10488,28 @@
       <c r="A268" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B268" s="7" t="s">
+      <c r="B268" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C268" s="7" t="s">
+      <c r="C268" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D268" s="7" t="s">
+      <c r="D268" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E268" s="7" t="s">
+      <c r="E268" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F268" s="7" t="s">
+      <c r="F268" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G268" s="7">
+      <c r="G268" s="6">
         <v>21</v>
       </c>
-      <c r="H268" s="7" t="s">
+      <c r="H268" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I268" s="7" t="s">
+      <c r="I268" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10169,28 +10517,28 @@
       <c r="A269" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="B269" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C269" s="7" t="s">
+      <c r="C269" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D269" s="7" t="s">
+      <c r="D269" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E269" s="7" t="s">
+      <c r="E269" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F269" s="7" t="s">
+      <c r="F269" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G269" s="7">
-        <v>1</v>
-      </c>
-      <c r="H269" s="7" t="s">
+      <c r="G269" s="6">
+        <v>1</v>
+      </c>
+      <c r="H269" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I269" s="7" t="s">
+      <c r="I269" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10198,28 +10546,28 @@
       <c r="A270" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B270" s="7" t="s">
+      <c r="B270" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C270" s="7" t="s">
+      <c r="C270" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D270" s="7" t="s">
+      <c r="D270" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E270" s="7" t="s">
+      <c r="E270" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="F270" s="7" t="s">
+      <c r="F270" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G270" s="7">
+      <c r="G270" s="6">
         <v>2</v>
       </c>
-      <c r="H270" s="7" t="s">
+      <c r="H270" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I270" s="7" t="s">
+      <c r="I270" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10227,28 +10575,28 @@
       <c r="A271" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C271" s="7" t="s">
+      <c r="C271" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D271" s="7" t="s">
+      <c r="D271" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E271" s="7" t="s">
+      <c r="E271" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F271" s="7" t="s">
+      <c r="F271" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G271" s="7">
+      <c r="G271" s="6">
         <v>12</v>
       </c>
-      <c r="H271" s="7" t="s">
+      <c r="H271" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I271" s="7" t="s">
+      <c r="I271" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10256,28 +10604,28 @@
       <c r="A272" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B272" s="7" t="s">
+      <c r="B272" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C272" s="7" t="s">
+      <c r="C272" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D272" s="7" t="s">
+      <c r="D272" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E272" s="7" t="s">
+      <c r="E272" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F272" s="7" t="s">
+      <c r="F272" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G272" s="7">
-        <v>1</v>
-      </c>
-      <c r="H272" s="7" t="s">
+      <c r="G272" s="6">
+        <v>1</v>
+      </c>
+      <c r="H272" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I272" s="7" t="s">
+      <c r="I272" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10285,28 +10633,28 @@
       <c r="A273" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B273" s="7" t="s">
+      <c r="B273" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C273" s="7" t="s">
+      <c r="C273" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D273" s="7" t="s">
+      <c r="D273" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E273" s="7" t="s">
+      <c r="E273" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F273" s="7" t="s">
+      <c r="F273" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G273" s="7">
+      <c r="G273" s="6">
         <v>2</v>
       </c>
-      <c r="H273" s="7" t="s">
+      <c r="H273" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I273" s="7" t="s">
+      <c r="I273" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10314,28 +10662,28 @@
       <c r="A274" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B274" s="7" t="s">
+      <c r="B274" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C274" s="7" t="s">
+      <c r="C274" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D274" s="7" t="s">
+      <c r="D274" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E274" s="7" t="s">
+      <c r="E274" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F274" s="7" t="s">
+      <c r="F274" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G274" s="7">
+      <c r="G274" s="6">
         <v>19</v>
       </c>
-      <c r="H274" s="7" t="s">
+      <c r="H274" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="I274" s="7" t="s">
+      <c r="I274" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -10343,28 +10691,28 @@
       <c r="A275" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B275" s="7" t="s">
+      <c r="B275" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C275" s="7" t="s">
+      <c r="C275" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D275" s="7" t="s">
+      <c r="D275" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E275" s="7" t="s">
+      <c r="E275" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F275" s="7" t="s">
+      <c r="F275" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G275" s="7">
+      <c r="G275" s="6">
         <v>4</v>
       </c>
-      <c r="H275" s="7" t="s">
+      <c r="H275" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="I275" s="7" t="s">
+      <c r="I275" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -10372,28 +10720,28 @@
       <c r="A276" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C276" s="7" t="s">
+      <c r="C276" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D276" s="7" t="s">
+      <c r="D276" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E276" s="7" t="s">
+      <c r="E276" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F276" s="7" t="s">
+      <c r="F276" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G276" s="7">
-        <v>1</v>
-      </c>
-      <c r="H276" s="7" t="s">
+      <c r="G276" s="6">
+        <v>1</v>
+      </c>
+      <c r="H276" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="I276" s="7" t="s">
+      <c r="I276" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -10401,28 +10749,28 @@
       <c r="A277" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B277" s="7" t="s">
+      <c r="B277" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C277" s="7" t="s">
+      <c r="C277" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D277" s="7" t="s">
+      <c r="D277" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E277" s="7" t="s">
+      <c r="E277" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="F277" s="7" t="s">
+      <c r="F277" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G277" s="7">
+      <c r="G277" s="6">
         <v>28</v>
       </c>
-      <c r="H277" s="7" t="s">
+      <c r="H277" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="I277" s="7" t="s">
+      <c r="I277" s="6" t="s">
         <v>332</v>
       </c>
     </row>
@@ -10430,28 +10778,28 @@
       <c r="A278" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="B278" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C278" s="7" t="s">
+      <c r="C278" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D278" s="7" t="s">
+      <c r="D278" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E278" s="7" t="s">
+      <c r="E278" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="F278" s="7" t="s">
+      <c r="F278" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G278" s="7">
+      <c r="G278" s="6">
         <v>24</v>
       </c>
-      <c r="H278" s="7" t="s">
+      <c r="H278" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I278" s="7" t="s">
+      <c r="I278" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10459,28 +10807,28 @@
       <c r="A279" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B279" s="7" t="s">
+      <c r="B279" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C279" s="7" t="s">
+      <c r="C279" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D279" s="7" t="s">
+      <c r="D279" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E279" s="7" t="s">
+      <c r="E279" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="F279" s="7" t="s">
+      <c r="F279" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G279" s="7">
+      <c r="G279" s="6">
         <v>24</v>
       </c>
-      <c r="H279" s="7" t="s">
+      <c r="H279" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I279" s="7" t="s">
+      <c r="I279" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -10488,29 +10836,6873 @@
       <c r="A280" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B280" s="7" t="s">
+      <c r="B280" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C280" s="7" t="s">
+      <c r="C280" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="D280" s="7" t="s">
+      <c r="D280" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="E280" s="7" t="s">
+      <c r="E280" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F280" s="7" t="s">
+      <c r="F280" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G280" s="7">
+      <c r="G280" s="6">
         <v>21</v>
       </c>
-      <c r="H280" s="7" t="s">
+      <c r="H280" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="I280" s="7" t="s">
+      <c r="I280" s="6" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E281" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G281" s="7">
+        <v>27</v>
+      </c>
+      <c r="H281" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G282" s="7">
+        <v>29</v>
+      </c>
+      <c r="H282" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E283" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F283" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G283" s="7">
+        <v>27</v>
+      </c>
+      <c r="H283" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I283" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G284" s="7">
+        <v>27</v>
+      </c>
+      <c r="H284" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E285" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G285" s="7">
+        <v>1</v>
+      </c>
+      <c r="H285" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I285" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G286" s="7">
+        <v>1</v>
+      </c>
+      <c r="H286" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
+      <c r="A287" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E287" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G287" s="7">
+        <v>23</v>
+      </c>
+      <c r="H287" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="I287" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E288" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G288" s="7">
+        <v>23</v>
+      </c>
+      <c r="H288" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E289" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G289" s="7">
+        <v>1</v>
+      </c>
+      <c r="H289" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="I289" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E290" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G290" s="7">
+        <v>1</v>
+      </c>
+      <c r="H290" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E291" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G291" s="7">
+        <v>8</v>
+      </c>
+      <c r="H291" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I291" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E292" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G292" s="7">
+        <v>19</v>
+      </c>
+      <c r="H292" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E293" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G293" s="7">
+        <v>19</v>
+      </c>
+      <c r="H293" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E294" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G294" s="7">
+        <v>19</v>
+      </c>
+      <c r="H294" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E295" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G295" s="7">
+        <v>12</v>
+      </c>
+      <c r="H295" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I295" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E296" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G296" s="7">
+        <v>16</v>
+      </c>
+      <c r="H296" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E297" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F297" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G297" s="7">
+        <v>23</v>
+      </c>
+      <c r="H297" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I297" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D298" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E298" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G298" s="7">
+        <v>10</v>
+      </c>
+      <c r="H298" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D299" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E299" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G299" s="7">
+        <v>22</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E300" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G300" s="7">
+        <v>1</v>
+      </c>
+      <c r="H300" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D301" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G301" s="7">
+        <v>1</v>
+      </c>
+      <c r="H301" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G302" s="7">
+        <v>1</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E303" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G303" s="7">
+        <v>30</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9">
+      <c r="A304" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G304" s="7">
+        <v>16</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
+      <c r="A305" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G305" s="7">
+        <v>19</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9">
+      <c r="A306" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G306" s="7">
+        <v>28</v>
+      </c>
+      <c r="H306" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
+      <c r="A307" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G307" s="7">
+        <v>19</v>
+      </c>
+      <c r="H307" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9">
+      <c r="A308" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G308" s="7">
+        <v>19</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9">
+      <c r="A309" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E309" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G309" s="7">
+        <v>21</v>
+      </c>
+      <c r="H309" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9">
+      <c r="A310" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G310" s="7">
+        <v>25</v>
+      </c>
+      <c r="H310" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9">
+      <c r="A311" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G311" s="7">
+        <v>19</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9">
+      <c r="A312" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G312" s="7">
+        <v>23</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9">
+      <c r="A313" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G313" s="7">
+        <v>21</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9">
+      <c r="A314" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G314" s="7">
+        <v>11</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9">
+      <c r="A315" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G315" s="7">
+        <v>1</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9">
+      <c r="A316" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G316" s="7">
+        <v>1</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9">
+      <c r="A317" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G317" s="7">
+        <v>9</v>
+      </c>
+      <c r="H317" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9">
+      <c r="A318" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G318" s="7">
+        <v>1</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9">
+      <c r="A319" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G319" s="7">
+        <v>9</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9">
+      <c r="A320" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G320" s="7">
+        <v>15</v>
+      </c>
+      <c r="H320" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9">
+      <c r="A321" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G321" s="7">
+        <v>1</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9">
+      <c r="A322" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C322" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D322" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G322" s="7">
+        <v>7</v>
+      </c>
+      <c r="H322" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
+      <c r="A323" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E323" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G323" s="7">
+        <v>24</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9">
+      <c r="A324" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E324" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G324" s="7">
+        <v>5</v>
+      </c>
+      <c r="H324" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9">
+      <c r="A325" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G325" s="7">
+        <v>12</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G326" s="7">
+        <v>7</v>
+      </c>
+      <c r="H326" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E327" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G327" s="7">
+        <v>11</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G328" s="7">
+        <v>19</v>
+      </c>
+      <c r="H328" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D329" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G329" s="7">
+        <v>17</v>
+      </c>
+      <c r="H329" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D330" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G330" s="7">
+        <v>7</v>
+      </c>
+      <c r="H330" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D331" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G331" s="7">
+        <v>21</v>
+      </c>
+      <c r="H331" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I331" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D332" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G332" s="7">
+        <v>22</v>
+      </c>
+      <c r="H332" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C333" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F333" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G333" s="7">
+        <v>22</v>
+      </c>
+      <c r="H333" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I333" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G334" s="7">
+        <v>14</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G335" s="7">
+        <v>22</v>
+      </c>
+      <c r="H335" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I335" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G336" s="7">
+        <v>2</v>
+      </c>
+      <c r="H336" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9">
+      <c r="A337" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C337" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D337" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E337" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G337" s="7">
+        <v>21</v>
+      </c>
+      <c r="H337" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I337" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9">
+      <c r="A338" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C338" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D338" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G338" s="7">
+        <v>17</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9">
+      <c r="A339" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C339" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D339" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G339" s="7">
+        <v>8</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C340" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G340" s="7">
+        <v>1</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D341" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G341" s="7">
+        <v>1</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G342" s="7">
+        <v>10</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G343" s="7">
+        <v>18</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G344" s="7">
+        <v>16</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C345" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D345" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E345" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G345" s="7">
+        <v>13</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D346" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E346" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G346" s="7">
+        <v>5</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C347" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D347" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E347" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G347" s="7">
+        <v>17</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D348" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E348" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G348" s="7">
+        <v>14</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D349" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E349" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G349" s="7">
+        <v>12</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C350" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D350" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E350" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G350" s="7">
+        <v>11</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D351" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E351" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G351" s="7">
+        <v>21</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D352" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E352" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G352" s="7">
+        <v>11</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C353" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D353" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E353" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G353" s="7">
+        <v>1</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D354" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G354" s="7">
+        <v>2</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G355" s="7">
+        <v>19</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C356" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D356" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E356" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G356" s="7">
+        <v>2</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D357" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E357" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G357" s="7">
+        <v>16</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C358" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D358" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E358" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G358" s="7">
+        <v>6</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D359" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E359" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G359" s="7">
+        <v>1</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D360" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E360" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G360" s="7">
+        <v>1</v>
+      </c>
+      <c r="H360" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C361" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D361" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E361" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G361" s="7">
+        <v>1</v>
+      </c>
+      <c r="H361" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C362" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D362" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E362" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G362" s="7">
+        <v>1</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D363" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G363" s="7">
+        <v>1</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C364" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D364" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G364" s="7">
+        <v>12</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G365" s="7">
+        <v>28</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D366" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E366" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G366" s="7">
+        <v>1</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D367" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E367" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G367" s="7">
+        <v>1</v>
+      </c>
+      <c r="H367" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D368" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E368" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G368" s="7">
+        <v>21</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D369" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G369" s="7">
+        <v>30</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I369" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D370" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E370" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G370" s="7">
+        <v>30</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E371" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G371" s="7">
+        <v>3</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E372" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G372" s="7">
+        <v>28</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E373" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G373" s="7">
+        <v>3</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I373" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E374" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G374" s="7">
+        <v>3</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C375" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E375" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F375" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G375" s="7">
+        <v>28</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I375" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F376" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G376" s="7">
+        <v>32</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D377" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F377" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G377" s="7">
+        <v>1</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I377" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C378" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F378" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G378" s="7">
+        <v>21</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F379" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G379" s="7">
+        <v>1</v>
+      </c>
+      <c r="H379" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I379" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F380" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G380" s="7">
+        <v>30</v>
+      </c>
+      <c r="H380" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C381" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G381" s="7">
+        <v>29</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I381" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D382" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="F382" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G382" s="7">
+        <v>2</v>
+      </c>
+      <c r="H382" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F383" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G383" s="7">
+        <v>6</v>
+      </c>
+      <c r="H383" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I383" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C384" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D384" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F384" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G384" s="7">
+        <v>2</v>
+      </c>
+      <c r="H384" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I384" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G385" s="7">
+        <v>9</v>
+      </c>
+      <c r="H385" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I385" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C386" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="F386" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G386" s="7">
+        <v>1</v>
+      </c>
+      <c r="H386" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C387" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F387" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G387" s="7">
+        <v>30</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I387" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F388" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G388" s="7">
+        <v>31</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I388" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C389" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D389" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E389" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F389" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G389" s="7">
+        <v>23</v>
+      </c>
+      <c r="H389" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I389" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G390" s="7">
+        <v>3</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I390" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D391" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E391" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F391" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G391" s="7">
+        <v>3</v>
+      </c>
+      <c r="H391" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I391" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F392" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G392" s="7">
+        <v>26</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I392" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9">
+      <c r="A393" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F393" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G393" s="7">
+        <v>1</v>
+      </c>
+      <c r="H393" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I393" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G394" s="7">
+        <v>1</v>
+      </c>
+      <c r="H394" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I394" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D395" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G395" s="7">
+        <v>30</v>
+      </c>
+      <c r="H395" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I395" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C396" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D396" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G396" s="7">
+        <v>21</v>
+      </c>
+      <c r="H396" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I396" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="G397" s="7">
+        <v>25</v>
+      </c>
+      <c r="H397" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I397" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C398" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D398" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E398" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G398" s="7">
+        <v>33</v>
+      </c>
+      <c r="H398" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I398" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C399" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D399" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E399" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F399" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G399" s="7">
+        <v>2</v>
+      </c>
+      <c r="H399" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I399" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C400" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D400" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F400" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G400" s="7">
+        <v>31</v>
+      </c>
+      <c r="H400" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I400" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D401" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G401" s="7">
+        <v>32</v>
+      </c>
+      <c r="H401" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I401" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9">
+      <c r="A402" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C402" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D402" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E402" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G402" s="7">
+        <v>1</v>
+      </c>
+      <c r="H402" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I402" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9">
+      <c r="A403" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D403" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E403" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G403" s="7">
+        <v>1</v>
+      </c>
+      <c r="H403" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I403" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9">
+      <c r="A404" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D404" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E404" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="G404" s="7">
+        <v>1</v>
+      </c>
+      <c r="H404" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I404" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9">
+      <c r="A405" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E405" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G405" s="7">
+        <v>33</v>
+      </c>
+      <c r="H405" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I405" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9">
+      <c r="A406" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D406" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E406" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G406" s="7">
+        <v>1</v>
+      </c>
+      <c r="H406" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I406" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9">
+      <c r="A407" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D407" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E407" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G407" s="7">
+        <v>1</v>
+      </c>
+      <c r="H407" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I407" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9">
+      <c r="A408" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E408" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G408" s="7">
+        <v>1</v>
+      </c>
+      <c r="H408" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I408" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9">
+      <c r="A409" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D409" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E409" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G409" s="7">
+        <v>1</v>
+      </c>
+      <c r="H409" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I409" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9">
+      <c r="A410" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D410" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E410" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G410" s="7">
+        <v>1</v>
+      </c>
+      <c r="H410" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I410" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9">
+      <c r="A411" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D411" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E411" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G411" s="7">
+        <v>33</v>
+      </c>
+      <c r="H411" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I411" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9">
+      <c r="A412" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D412" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E412" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G412" s="7">
+        <v>33</v>
+      </c>
+      <c r="H412" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I412" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9">
+      <c r="A413" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C413" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D413" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E413" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G413" s="7">
+        <v>1</v>
+      </c>
+      <c r="H413" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I413" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9">
+      <c r="A414" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C414" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D414" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E414" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G414" s="7">
+        <v>2</v>
+      </c>
+      <c r="H414" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I414" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9">
+      <c r="A415" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D415" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E415" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G415" s="7">
+        <v>1</v>
+      </c>
+      <c r="H415" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I415" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9">
+      <c r="A416" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D416" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E416" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G416" s="7">
+        <v>2</v>
+      </c>
+      <c r="H416" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I416" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9">
+      <c r="A417" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D417" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E417" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G417" s="7">
+        <v>1</v>
+      </c>
+      <c r="H417" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I417" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9">
+      <c r="A418" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D418" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E418" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G418" s="7">
+        <v>1</v>
+      </c>
+      <c r="H418" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I418" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9">
+      <c r="A419" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D419" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E419" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G419" s="7">
+        <v>1</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I419" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9">
+      <c r="A420" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D420" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E420" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G420" s="7">
+        <v>33</v>
+      </c>
+      <c r="H420" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I420" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9">
+      <c r="A421" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D421" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E421" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G421" s="7">
+        <v>34</v>
+      </c>
+      <c r="H421" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I421" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9">
+      <c r="A422" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D422" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E422" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G422" s="7">
+        <v>34</v>
+      </c>
+      <c r="H422" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I422" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9">
+      <c r="A423" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D423" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E423" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G423" s="7">
+        <v>1</v>
+      </c>
+      <c r="H423" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I423" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9">
+      <c r="A424" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D424" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E424" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F424" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G424" s="7">
+        <v>2</v>
+      </c>
+      <c r="H424" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I424" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9">
+      <c r="A425" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D425" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F425" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G425" s="7">
+        <v>1</v>
+      </c>
+      <c r="H425" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I425" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9">
+      <c r="A426" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D426" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E426" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F426" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G426" s="7">
+        <v>1</v>
+      </c>
+      <c r="H426" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I426" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9">
+      <c r="A427" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D427" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E427" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F427" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G427" s="7">
+        <v>1</v>
+      </c>
+      <c r="H427" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I427" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9">
+      <c r="A428" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E428" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F428" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G428" s="7">
+        <v>3</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I428" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9">
+      <c r="A429" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E429" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G429" s="7">
+        <v>1</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I429" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9">
+      <c r="A430" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E430" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G430" s="7">
+        <v>31</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9">
+      <c r="A431" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D431" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E431" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G431" s="7">
+        <v>29</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9">
+      <c r="A432" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D432" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E432" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="G432" s="7">
+        <v>33</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9">
+      <c r="A433" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D433" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E433" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G433" s="7">
+        <v>29</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9">
+      <c r="A434" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D434" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E434" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G434" s="7">
+        <v>32</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9">
+      <c r="A435" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D435" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E435" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G435" s="7">
+        <v>32</v>
+      </c>
+      <c r="H435" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9">
+      <c r="A436" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D436" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E436" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G436" s="7">
+        <v>1</v>
+      </c>
+      <c r="H436" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9">
+      <c r="A437" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D437" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E437" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F437" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G437" s="7">
+        <v>1</v>
+      </c>
+      <c r="H437" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I437" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9">
+      <c r="A438" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D438" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E438" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F438" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G438" s="7">
+        <v>1</v>
+      </c>
+      <c r="H438" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I438" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9">
+      <c r="A439" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D439" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E439" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G439" s="7">
+        <v>2</v>
+      </c>
+      <c r="H439" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I439" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9">
+      <c r="A440" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D440" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E440" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G440" s="7">
+        <v>1</v>
+      </c>
+      <c r="H440" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I440" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9">
+      <c r="A441" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D441" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E441" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G441" s="7">
+        <v>1</v>
+      </c>
+      <c r="H441" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I441" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9">
+      <c r="A442" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D442" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E442" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="F442" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G442" s="7">
+        <v>32</v>
+      </c>
+      <c r="H442" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9">
+      <c r="A443" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D443" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E443" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F443" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G443" s="7">
+        <v>29</v>
+      </c>
+      <c r="H443" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I443" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9">
+      <c r="A444" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D444" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E444" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F444" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G444" s="7">
+        <v>28</v>
+      </c>
+      <c r="H444" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I444" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9">
+      <c r="A445" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D445" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E445" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F445" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G445" s="7">
+        <v>33</v>
+      </c>
+      <c r="H445" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I445" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9">
+      <c r="A446" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D446" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E446" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F446" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G446" s="7">
+        <v>1</v>
+      </c>
+      <c r="H446" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I446" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9">
+      <c r="A447" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D447" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E447" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="F447" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G447" s="7">
+        <v>35</v>
+      </c>
+      <c r="H447" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I447" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9">
+      <c r="A448" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D448" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E448" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G448" s="7">
+        <v>1</v>
+      </c>
+      <c r="H448" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I448" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9">
+      <c r="A449" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D449" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E449" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G449" s="7">
+        <v>34</v>
+      </c>
+      <c r="H449" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I449" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9">
+      <c r="A450" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D450" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E450" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F450" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G450" s="7">
+        <v>1</v>
+      </c>
+      <c r="H450" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I450" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9">
+      <c r="A451" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D451" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E451" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F451" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G451" s="7">
+        <v>3</v>
+      </c>
+      <c r="H451" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I451" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9">
+      <c r="A452" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D452" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E452" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G452" s="7">
+        <v>1</v>
+      </c>
+      <c r="H452" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I452" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9">
+      <c r="A453" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D453" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E453" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F453" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G453" s="7">
+        <v>1</v>
+      </c>
+      <c r="H453" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I453" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9">
+      <c r="A454" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D454" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E454" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F454" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G454" s="7">
+        <v>31</v>
+      </c>
+      <c r="H454" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I454" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9">
+      <c r="A455" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D455" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E455" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F455" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G455" s="7">
+        <v>30</v>
+      </c>
+      <c r="H455" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I455" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9">
+      <c r="A456" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D456" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E456" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G456" s="7">
+        <v>28</v>
+      </c>
+      <c r="H456" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I456" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9">
+      <c r="A457" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D457" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E457" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G457" s="7">
+        <v>1</v>
+      </c>
+      <c r="H457" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I457" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9">
+      <c r="A458" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D458" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E458" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F458" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G458" s="7">
+        <v>2</v>
+      </c>
+      <c r="H458" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I458" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9">
+      <c r="A459" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D459" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E459" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F459" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G459" s="7">
+        <v>1</v>
+      </c>
+      <c r="H459" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I459" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9">
+      <c r="A460" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D460" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E460" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F460" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G460" s="7">
+        <v>1</v>
+      </c>
+      <c r="H460" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I460" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9">
+      <c r="A461" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D461" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E461" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G461" s="7">
+        <v>1</v>
+      </c>
+      <c r="H461" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I461" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9">
+      <c r="A462" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D462" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E462" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F462" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G462" s="7">
+        <v>1</v>
+      </c>
+      <c r="H462" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I462" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9">
+      <c r="A463" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D463" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E463" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F463" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G463" s="7">
+        <v>30</v>
+      </c>
+      <c r="H463" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I463" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9">
+      <c r="A464" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D464" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E464" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F464" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G464" s="7">
+        <v>28</v>
+      </c>
+      <c r="H464" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I464" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9">
+      <c r="A465" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D465" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E465" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F465" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G465" s="7">
+        <v>32</v>
+      </c>
+      <c r="H465" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I465" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9">
+      <c r="A466" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D466" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E466" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="F466" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G466" s="7">
+        <v>15</v>
+      </c>
+      <c r="H466" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I466" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9">
+      <c r="A467" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D467" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E467" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="F467" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G467" s="7">
+        <v>10</v>
+      </c>
+      <c r="H467" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I467" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9">
+      <c r="A468" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D468" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E468" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F468" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G468" s="7">
+        <v>1</v>
+      </c>
+      <c r="H468" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I468" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9">
+      <c r="A469" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D469" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E469" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="F469" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G469" s="7">
+        <v>10</v>
+      </c>
+      <c r="H469" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I469" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9">
+      <c r="A470" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B470" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C470" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D470" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E470" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="F470" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G470" s="7">
+        <v>19</v>
+      </c>
+      <c r="H470" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I470" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9">
+      <c r="A471" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B471" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C471" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D471" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E471" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F471" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G471" s="7">
+        <v>21</v>
+      </c>
+      <c r="H471" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I471" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9">
+      <c r="A472" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C472" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D472" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E472" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F472" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G472" s="7">
+        <v>4</v>
+      </c>
+      <c r="H472" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I472" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9">
+      <c r="A473" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C473" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D473" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E473" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F473" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G473" s="7">
+        <v>1</v>
+      </c>
+      <c r="H473" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I473" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9">
+      <c r="A474" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C474" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D474" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E474" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F474" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G474" s="7">
+        <v>1</v>
+      </c>
+      <c r="H474" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I474" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9">
+      <c r="A475" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C475" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D475" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E475" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F475" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G475" s="7">
+        <v>1</v>
+      </c>
+      <c r="H475" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I475" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9">
+      <c r="A476" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B476" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C476" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D476" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E476" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F476" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G476" s="7">
+        <v>4</v>
+      </c>
+      <c r="H476" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I476" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9">
+      <c r="A477" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B477" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C477" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D477" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E477" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F477" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G477" s="7">
+        <v>1</v>
+      </c>
+      <c r="H477" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I477" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9">
+      <c r="A478" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C478" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D478" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E478" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F478" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G478" s="7">
+        <v>3</v>
+      </c>
+      <c r="H478" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I478" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9">
+      <c r="A479" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B479" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C479" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D479" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E479" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F479" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G479" s="7">
+        <v>1</v>
+      </c>
+      <c r="H479" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I479" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9">
+      <c r="A480" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C480" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D480" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E480" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F480" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G480" s="7">
+        <v>3</v>
+      </c>
+      <c r="H480" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I480" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9">
+      <c r="A481" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B481" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C481" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D481" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E481" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F481" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G481" s="7">
+        <v>3</v>
+      </c>
+      <c r="H481" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I481" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9">
+      <c r="A482" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D482" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E482" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="F482" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G482" s="7">
+        <v>1</v>
+      </c>
+      <c r="H482" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I482" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9">
+      <c r="A483" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B483" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C483" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D483" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E483" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F483" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G483" s="7">
+        <v>2</v>
+      </c>
+      <c r="H483" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I483" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9">
+      <c r="A484" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B484" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C484" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D484" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E484" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F484" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G484" s="7">
+        <v>1</v>
+      </c>
+      <c r="H484" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I484" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9">
+      <c r="A485" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B485" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C485" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D485" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E485" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F485" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G485" s="7">
+        <v>1</v>
+      </c>
+      <c r="H485" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I485" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9">
+      <c r="A486" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B486" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C486" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D486" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E486" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F486" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G486" s="7">
+        <v>1</v>
+      </c>
+      <c r="H486" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I486" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9">
+      <c r="A487" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B487" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C487" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D487" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E487" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F487" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G487" s="7">
+        <v>1</v>
+      </c>
+      <c r="H487" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I487" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9">
+      <c r="A488" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B488" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C488" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D488" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="E488" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F488" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G488" s="7">
+        <v>2</v>
+      </c>
+      <c r="H488" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I488" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9">
+      <c r="A489" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B489" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C489" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D489" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E489" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G489" s="7">
+        <v>1</v>
+      </c>
+      <c r="H489" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I489" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9">
+      <c r="A490" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B490" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C490" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D490" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E490" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F490" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G490" s="7">
+        <v>1</v>
+      </c>
+      <c r="H490" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I490" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9">
+      <c r="A491" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B491" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C491" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D491" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E491" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F491" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G491" s="7">
+        <v>1</v>
+      </c>
+      <c r="H491" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I491" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9">
+      <c r="A492" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B492" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C492" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D492" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E492" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F492" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G492" s="7">
+        <v>2</v>
+      </c>
+      <c r="H492" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I492" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9">
+      <c r="A493" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B493" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C493" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D493" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E493" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F493" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G493" s="7">
+        <v>2</v>
+      </c>
+      <c r="H493" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I493" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9">
+      <c r="A494" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B494" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C494" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D494" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E494" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F494" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G494" s="7">
+        <v>2</v>
+      </c>
+      <c r="H494" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I494" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9">
+      <c r="A495" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B495" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C495" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D495" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E495" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F495" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G495" s="7">
+        <v>2</v>
+      </c>
+      <c r="H495" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I495" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9">
+      <c r="A496" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B496" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C496" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D496" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E496" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F496" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G496" s="7">
+        <v>1</v>
+      </c>
+      <c r="H496" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I496" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9">
+      <c r="A497" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C497" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D497" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E497" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F497" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G497" s="7">
+        <v>1</v>
+      </c>
+      <c r="H497" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I497" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9">
+      <c r="A498" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B498" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C498" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D498" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E498" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F498" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G498" s="7">
+        <v>4</v>
+      </c>
+      <c r="H498" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I498" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9">
+      <c r="A499" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B499" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C499" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D499" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E499" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F499" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G499" s="7">
+        <v>4</v>
+      </c>
+      <c r="H499" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I499" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9">
+      <c r="A500" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B500" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C500" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D500" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E500" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F500" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G500" s="7">
+        <v>3</v>
+      </c>
+      <c r="H500" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I500" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9">
+      <c r="A501" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B501" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C501" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D501" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E501" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F501" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G501" s="7">
+        <v>5</v>
+      </c>
+      <c r="H501" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I501" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9">
+      <c r="A502" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B502" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C502" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D502" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E502" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F502" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G502" s="7">
+        <v>1</v>
+      </c>
+      <c r="H502" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I502" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9">
+      <c r="A503" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B503" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C503" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D503" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E503" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F503" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G503" s="7">
+        <v>1</v>
+      </c>
+      <c r="H503" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I503" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9">
+      <c r="A504" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B504" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C504" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D504" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E504" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F504" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G504" s="7">
+        <v>1</v>
+      </c>
+      <c r="H504" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I504" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9">
+      <c r="A505" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B505" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C505" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D505" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E505" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F505" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G505" s="7">
+        <v>1</v>
+      </c>
+      <c r="H505" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I505" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9">
+      <c r="A506" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B506" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C506" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D506" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E506" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F506" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G506" s="7">
+        <v>1</v>
+      </c>
+      <c r="H506" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I506" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9">
+      <c r="A507" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B507" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C507" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D507" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E507" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="F507" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G507" s="7">
+        <v>2</v>
+      </c>
+      <c r="H507" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I507" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9">
+      <c r="A508" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B508" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C508" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D508" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E508" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="F508" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G508" s="7">
+        <v>7</v>
+      </c>
+      <c r="H508" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I508" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9">
+      <c r="A509" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B509" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C509" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D509" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E509" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F509" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G509" s="7">
+        <v>4</v>
+      </c>
+      <c r="H509" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I509" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9">
+      <c r="A510" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B510" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C510" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D510" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E510" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F510" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G510" s="7">
+        <v>1</v>
+      </c>
+      <c r="H510" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I510" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9">
+      <c r="A511" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B511" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C511" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D511" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E511" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F511" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G511" s="7">
+        <v>2</v>
+      </c>
+      <c r="H511" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I511" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9">
+      <c r="A512" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B512" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C512" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D512" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E512" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F512" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G512" s="7">
+        <v>1</v>
+      </c>
+      <c r="H512" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I512" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9">
+      <c r="A513" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B513" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C513" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D513" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E513" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F513" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G513" s="7">
+        <v>1</v>
+      </c>
+      <c r="H513" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I513" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9">
+      <c r="A514" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B514" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C514" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D514" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E514" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="F514" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G514" s="7">
+        <v>3</v>
+      </c>
+      <c r="H514" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I514" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9">
+      <c r="A515" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B515" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C515" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="D515" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="E515" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F515" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G515" s="7">
+        <v>2</v>
+      </c>
+      <c r="H515" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I515" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9">
+      <c r="A516" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B516" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C516" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="D516" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="E516" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="F516" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="G516" s="6">
+        <v>32</v>
+      </c>
+      <c r="H516" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="I516" s="6" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1522</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12177" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12425" uniqueCount="1017">
   <si>
     <t>校区</t>
   </si>
@@ -3048,6 +3048,39 @@
   </si>
   <si>
     <t>B230806</t>
+  </si>
+  <si>
+    <t>TX136603S</t>
+  </si>
+  <si>
+    <t>广播电视设备与节目制作技术</t>
+  </si>
+  <si>
+    <t>刘浏/李欣2</t>
+  </si>
+  <si>
+    <t>B220126</t>
+  </si>
+  <si>
+    <t>TX116401S</t>
+  </si>
+  <si>
+    <t>OpticalFiberCommunicationSystem</t>
+  </si>
+  <si>
+    <t>齐丽娜</t>
+  </si>
+  <si>
+    <t>蔡安亮</t>
+  </si>
+  <si>
+    <t>陈健</t>
+  </si>
+  <si>
+    <t>王金元</t>
+  </si>
+  <si>
+    <t>OpticalFiberCommunicationSystem(全英文授课）</t>
   </si>
 </sst>
 </file>
@@ -4236,7 +4269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1522"/>
+  <dimension ref="A1:I1553"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -45144,28 +45177,28 @@
       <c r="A1411" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1411" s="7" t="s">
+      <c r="B1411" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1411" s="7" t="s">
+      <c r="C1411" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="D1411" s="7" t="s">
+      <c r="D1411" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="E1411" s="7" t="s">
+      <c r="E1411" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="F1411" s="7" t="s">
+      <c r="F1411" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="G1411" s="7">
+      <c r="G1411" s="6">
         <v>32</v>
       </c>
-      <c r="H1411" s="7" t="s">
+      <c r="H1411" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="I1411" s="7" t="s">
+      <c r="I1411" s="6" t="s">
         <v>584</v>
       </c>
     </row>
@@ -45173,28 +45206,28 @@
       <c r="A1412" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1412" s="7" t="s">
+      <c r="B1412" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1412" s="7" t="s">
+      <c r="C1412" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="D1412" s="7" t="s">
+      <c r="D1412" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="E1412" s="7" t="s">
+      <c r="E1412" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="F1412" s="7" t="s">
+      <c r="F1412" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="G1412" s="7">
+      <c r="G1412" s="6">
         <v>29</v>
       </c>
-      <c r="H1412" s="7" t="s">
+      <c r="H1412" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="I1412" s="7" t="s">
+      <c r="I1412" s="6" t="s">
         <v>584</v>
       </c>
     </row>
@@ -45202,28 +45235,28 @@
       <c r="A1413" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1413" s="7" t="s">
+      <c r="B1413" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1413" s="7" t="s">
+      <c r="C1413" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="D1413" s="7" t="s">
+      <c r="D1413" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="E1413" s="7" t="s">
+      <c r="E1413" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="F1413" s="7" t="s">
+      <c r="F1413" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="G1413" s="7">
+      <c r="G1413" s="6">
         <v>2</v>
       </c>
-      <c r="H1413" s="7" t="s">
+      <c r="H1413" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="I1413" s="7" t="s">
+      <c r="I1413" s="6" t="s">
         <v>904</v>
       </c>
     </row>
@@ -45231,28 +45264,28 @@
       <c r="A1414" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1414" s="7" t="s">
+      <c r="B1414" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1414" s="7" t="s">
+      <c r="C1414" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="D1414" s="7" t="s">
+      <c r="D1414" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="E1414" s="7" t="s">
+      <c r="E1414" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="F1414" s="7" t="s">
+      <c r="F1414" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="G1414" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1414" s="7" t="s">
+      <c r="G1414" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1414" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="I1414" s="7" t="s">
+      <c r="I1414" s="6" t="s">
         <v>904</v>
       </c>
     </row>
@@ -45260,28 +45293,28 @@
       <c r="A1415" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1415" s="7" t="s">
+      <c r="B1415" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1415" s="7" t="s">
+      <c r="C1415" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="D1415" s="7" t="s">
+      <c r="D1415" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="E1415" s="7" t="s">
+      <c r="E1415" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="F1415" s="7" t="s">
+      <c r="F1415" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="G1415" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1415" s="7" t="s">
+      <c r="G1415" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1415" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="I1415" s="7" t="s">
+      <c r="I1415" s="6" t="s">
         <v>904</v>
       </c>
     </row>
@@ -45289,28 +45322,28 @@
       <c r="A1416" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1416" s="7" t="s">
+      <c r="B1416" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1416" s="7" t="s">
+      <c r="C1416" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="D1416" s="7" t="s">
+      <c r="D1416" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="E1416" s="7" t="s">
+      <c r="E1416" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="F1416" s="7" t="s">
+      <c r="F1416" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="G1416" s="7">
+      <c r="G1416" s="6">
         <v>3</v>
       </c>
-      <c r="H1416" s="7" t="s">
+      <c r="H1416" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="I1416" s="7" t="s">
+      <c r="I1416" s="6" t="s">
         <v>904</v>
       </c>
     </row>
@@ -45318,28 +45351,28 @@
       <c r="A1417" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1417" s="7" t="s">
+      <c r="B1417" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1417" s="7" t="s">
+      <c r="C1417" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="D1417" s="7" t="s">
+      <c r="D1417" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="E1417" s="7" t="s">
+      <c r="E1417" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="F1417" s="7" t="s">
+      <c r="F1417" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="G1417" s="7">
+      <c r="G1417" s="6">
         <v>2</v>
       </c>
-      <c r="H1417" s="7" t="s">
+      <c r="H1417" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="I1417" s="7" t="s">
+      <c r="I1417" s="6" t="s">
         <v>904</v>
       </c>
     </row>
@@ -45347,28 +45380,28 @@
       <c r="A1418" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1418" s="7" t="s">
+      <c r="B1418" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1418" s="7" t="s">
+      <c r="C1418" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="D1418" s="7" t="s">
+      <c r="D1418" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="E1418" s="7" t="s">
+      <c r="E1418" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="F1418" s="7" t="s">
+      <c r="F1418" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="G1418" s="7">
+      <c r="G1418" s="6">
         <v>23</v>
       </c>
-      <c r="H1418" s="7" t="s">
+      <c r="H1418" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="I1418" s="7" t="s">
+      <c r="I1418" s="6" t="s">
         <v>913</v>
       </c>
     </row>
@@ -45376,28 +45409,28 @@
       <c r="A1419" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1419" s="7" t="s">
+      <c r="B1419" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C1419" s="7" t="s">
+      <c r="C1419" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="D1419" s="7" t="s">
+      <c r="D1419" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="E1419" s="7" t="s">
+      <c r="E1419" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="F1419" s="7" t="s">
+      <c r="F1419" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="G1419" s="7">
+      <c r="G1419" s="6">
         <v>25</v>
       </c>
-      <c r="H1419" s="7" t="s">
+      <c r="H1419" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="I1419" s="7" t="s">
+      <c r="I1419" s="6" t="s">
         <v>913</v>
       </c>
     </row>
@@ -45405,28 +45438,28 @@
       <c r="A1420" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1420" s="7" t="s">
+      <c r="B1420" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1420" s="7" t="s">
+      <c r="C1420" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1420" s="7" t="s">
+      <c r="D1420" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1420" s="7" t="s">
+      <c r="E1420" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F1420" s="7" t="s">
+      <c r="F1420" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1420" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1420" s="7" t="s">
+      <c r="G1420" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1420" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1420" s="7" t="s">
+      <c r="I1420" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45434,28 +45467,28 @@
       <c r="A1421" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1421" s="7" t="s">
+      <c r="B1421" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1421" s="7" t="s">
+      <c r="C1421" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1421" s="7" t="s">
+      <c r="D1421" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1421" s="7" t="s">
+      <c r="E1421" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F1421" s="7" t="s">
+      <c r="F1421" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1421" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1421" s="7" t="s">
+      <c r="G1421" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1421" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1421" s="7" t="s">
+      <c r="I1421" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45463,28 +45496,28 @@
       <c r="A1422" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1422" s="7" t="s">
+      <c r="B1422" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1422" s="7" t="s">
+      <c r="C1422" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1422" s="7" t="s">
+      <c r="D1422" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1422" s="7" t="s">
+      <c r="E1422" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="F1422" s="7" t="s">
+      <c r="F1422" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1422" s="7">
+      <c r="G1422" s="6">
         <v>24</v>
       </c>
-      <c r="H1422" s="7" t="s">
+      <c r="H1422" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1422" s="7" t="s">
+      <c r="I1422" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45492,28 +45525,28 @@
       <c r="A1423" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1423" s="7" t="s">
+      <c r="B1423" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1423" s="7" t="s">
+      <c r="C1423" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1423" s="7" t="s">
+      <c r="D1423" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1423" s="7" t="s">
+      <c r="E1423" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="F1423" s="7" t="s">
+      <c r="F1423" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1423" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1423" s="7" t="s">
+      <c r="G1423" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1423" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1423" s="7" t="s">
+      <c r="I1423" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45521,28 +45554,28 @@
       <c r="A1424" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1424" s="7" t="s">
+      <c r="B1424" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1424" s="7" t="s">
+      <c r="C1424" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1424" s="7" t="s">
+      <c r="D1424" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1424" s="7" t="s">
+      <c r="E1424" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="F1424" s="7" t="s">
+      <c r="F1424" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1424" s="7">
+      <c r="G1424" s="6">
         <v>24</v>
       </c>
-      <c r="H1424" s="7" t="s">
+      <c r="H1424" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1424" s="7" t="s">
+      <c r="I1424" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45550,28 +45583,28 @@
       <c r="A1425" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1425" s="7" t="s">
+      <c r="B1425" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1425" s="7" t="s">
+      <c r="C1425" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D1425" s="7" t="s">
+      <c r="D1425" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E1425" s="7" t="s">
+      <c r="E1425" s="6" t="s">
         <v>922</v>
       </c>
-      <c r="F1425" s="7" t="s">
+      <c r="F1425" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="G1425" s="7">
+      <c r="G1425" s="6">
         <v>12</v>
       </c>
-      <c r="H1425" s="7" t="s">
+      <c r="H1425" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1425" s="7" t="s">
+      <c r="I1425" s="6" t="s">
         <v>918</v>
       </c>
     </row>
@@ -45579,28 +45612,28 @@
       <c r="A1426" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1426" s="7" t="s">
+      <c r="B1426" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1426" s="7" t="s">
+      <c r="C1426" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="D1426" s="7" t="s">
+      <c r="D1426" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="E1426" s="7" t="s">
+      <c r="E1426" s="6" t="s">
         <v>925</v>
       </c>
-      <c r="F1426" s="7" t="s">
+      <c r="F1426" s="6" t="s">
         <v>926</v>
       </c>
-      <c r="G1426" s="7">
+      <c r="G1426" s="6">
         <v>25</v>
       </c>
-      <c r="H1426" s="7" t="s">
+      <c r="H1426" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1426" s="7" t="s">
+      <c r="I1426" s="6" t="s">
         <v>438</v>
       </c>
     </row>
@@ -45608,28 +45641,28 @@
       <c r="A1427" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1427" s="7" t="s">
+      <c r="B1427" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1427" s="7" t="s">
+      <c r="C1427" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="D1427" s="7" t="s">
+      <c r="D1427" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="E1427" s="7" t="s">
+      <c r="E1427" s="6" t="s">
         <v>927</v>
       </c>
-      <c r="F1427" s="7" t="s">
+      <c r="F1427" s="6" t="s">
         <v>926</v>
       </c>
-      <c r="G1427" s="7">
+      <c r="G1427" s="6">
         <v>25</v>
       </c>
-      <c r="H1427" s="7" t="s">
+      <c r="H1427" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1427" s="7" t="s">
+      <c r="I1427" s="6" t="s">
         <v>438</v>
       </c>
     </row>
@@ -45637,28 +45670,28 @@
       <c r="A1428" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1428" s="7" t="s">
+      <c r="B1428" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1428" s="7" t="s">
+      <c r="C1428" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="D1428" s="7" t="s">
+      <c r="D1428" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="E1428" s="7" t="s">
+      <c r="E1428" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F1428" s="7" t="s">
+      <c r="F1428" s="6" t="s">
         <v>928</v>
       </c>
-      <c r="G1428" s="7">
+      <c r="G1428" s="6">
         <v>25</v>
       </c>
-      <c r="H1428" s="7" t="s">
+      <c r="H1428" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1428" s="7" t="s">
+      <c r="I1428" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -45666,28 +45699,28 @@
       <c r="A1429" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1429" s="7" t="s">
+      <c r="B1429" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1429" s="7" t="s">
+      <c r="C1429" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="D1429" s="7" t="s">
+      <c r="D1429" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="E1429" s="7" t="s">
+      <c r="E1429" s="6" t="s">
         <v>929</v>
       </c>
-      <c r="F1429" s="7" t="s">
+      <c r="F1429" s="6" t="s">
         <v>928</v>
       </c>
-      <c r="G1429" s="7">
+      <c r="G1429" s="6">
         <v>25</v>
       </c>
-      <c r="H1429" s="7" t="s">
+      <c r="H1429" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1429" s="7" t="s">
+      <c r="I1429" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -45695,28 +45728,28 @@
       <c r="A1430" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1430" s="7" t="s">
+      <c r="B1430" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1430" s="7" t="s">
+      <c r="C1430" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="D1430" s="7" t="s">
+      <c r="D1430" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="E1430" s="7" t="s">
+      <c r="E1430" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="F1430" s="7" t="s">
+      <c r="F1430" s="6" t="s">
         <v>928</v>
       </c>
-      <c r="G1430" s="7">
+      <c r="G1430" s="6">
         <v>25</v>
       </c>
-      <c r="H1430" s="7" t="s">
+      <c r="H1430" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1430" s="7" t="s">
+      <c r="I1430" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -45724,28 +45757,28 @@
       <c r="A1431" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1431" s="7" t="s">
+      <c r="B1431" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1431" s="7" t="s">
+      <c r="C1431" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="D1431" s="7" t="s">
+      <c r="D1431" s="6" t="s">
         <v>932</v>
       </c>
-      <c r="E1431" s="7" t="s">
+      <c r="E1431" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F1431" s="7" t="s">
+      <c r="F1431" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="G1431" s="7">
+      <c r="G1431" s="6">
         <v>28</v>
       </c>
-      <c r="H1431" s="7" t="s">
+      <c r="H1431" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="I1431" s="7" t="s">
+      <c r="I1431" s="6" t="s">
         <v>934</v>
       </c>
     </row>
@@ -45753,28 +45786,28 @@
       <c r="A1432" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1432" s="7" t="s">
+      <c r="B1432" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1432" s="7" t="s">
+      <c r="C1432" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="D1432" s="7" t="s">
+      <c r="D1432" s="6" t="s">
         <v>932</v>
       </c>
-      <c r="E1432" s="7" t="s">
+      <c r="E1432" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F1432" s="7" t="s">
+      <c r="F1432" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="G1432" s="7">
+      <c r="G1432" s="6">
         <v>27</v>
       </c>
-      <c r="H1432" s="7" t="s">
+      <c r="H1432" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="I1432" s="7" t="s">
+      <c r="I1432" s="6" t="s">
         <v>934</v>
       </c>
     </row>
@@ -45782,28 +45815,28 @@
       <c r="A1433" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1433" s="7" t="s">
+      <c r="B1433" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1433" s="7" t="s">
+      <c r="C1433" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D1433" s="7" t="s">
+      <c r="D1433" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="E1433" s="7" t="s">
+      <c r="E1433" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F1433" s="7" t="s">
+      <c r="F1433" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="G1433" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1433" s="7" t="s">
+      <c r="G1433" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1433" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1433" s="7" t="s">
+      <c r="I1433" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -45811,28 +45844,28 @@
       <c r="A1434" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1434" s="7" t="s">
+      <c r="B1434" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1434" s="7" t="s">
+      <c r="C1434" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D1434" s="7" t="s">
+      <c r="D1434" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="E1434" s="7" t="s">
+      <c r="E1434" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F1434" s="7" t="s">
+      <c r="F1434" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="G1434" s="7">
+      <c r="G1434" s="6">
         <v>31</v>
       </c>
-      <c r="H1434" s="7" t="s">
+      <c r="H1434" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1434" s="7" t="s">
+      <c r="I1434" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -45840,28 +45873,28 @@
       <c r="A1435" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1435" s="7" t="s">
+      <c r="B1435" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1435" s="7" t="s">
+      <c r="C1435" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D1435" s="7" t="s">
+      <c r="D1435" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="E1435" s="7" t="s">
+      <c r="E1435" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F1435" s="7" t="s">
+      <c r="F1435" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="G1435" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1435" s="7" t="s">
+      <c r="G1435" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1435" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1435" s="7" t="s">
+      <c r="I1435" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -45869,28 +45902,28 @@
       <c r="A1436" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1436" s="7" t="s">
+      <c r="B1436" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1436" s="7" t="s">
+      <c r="C1436" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D1436" s="7" t="s">
+      <c r="D1436" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="E1436" s="7" t="s">
+      <c r="E1436" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="F1436" s="7" t="s">
+      <c r="F1436" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="G1436" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1436" s="7" t="s">
+      <c r="G1436" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1436" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="I1436" s="7" t="s">
+      <c r="I1436" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -45898,28 +45931,28 @@
       <c r="A1437" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1437" s="7" t="s">
+      <c r="B1437" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1437" s="7" t="s">
+      <c r="C1437" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="D1437" s="7" t="s">
+      <c r="D1437" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="E1437" s="7" t="s">
+      <c r="E1437" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F1437" s="7" t="s">
+      <c r="F1437" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="G1437" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1437" s="7" t="s">
+      <c r="G1437" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1437" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="I1437" s="7" t="s">
+      <c r="I1437" s="6" t="s">
         <v>942</v>
       </c>
     </row>
@@ -45927,28 +45960,28 @@
       <c r="A1438" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1438" s="7" t="s">
+      <c r="B1438" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1438" s="7" t="s">
+      <c r="C1438" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="D1438" s="7" t="s">
+      <c r="D1438" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="E1438" s="7" t="s">
+      <c r="E1438" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F1438" s="7" t="s">
+      <c r="F1438" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="G1438" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1438" s="7" t="s">
+      <c r="G1438" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1438" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="I1438" s="7" t="s">
+      <c r="I1438" s="6" t="s">
         <v>942</v>
       </c>
     </row>
@@ -45956,28 +45989,28 @@
       <c r="A1439" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1439" s="7" t="s">
+      <c r="B1439" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1439" s="7" t="s">
+      <c r="C1439" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="D1439" s="7" t="s">
+      <c r="D1439" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="E1439" s="7" t="s">
+      <c r="E1439" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F1439" s="7" t="s">
+      <c r="F1439" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="G1439" s="7">
+      <c r="G1439" s="6">
         <v>33</v>
       </c>
-      <c r="H1439" s="7" t="s">
+      <c r="H1439" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="I1439" s="7" t="s">
+      <c r="I1439" s="6" t="s">
         <v>942</v>
       </c>
     </row>
@@ -45985,28 +46018,28 @@
       <c r="A1440" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1440" s="7" t="s">
+      <c r="B1440" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1440" s="7" t="s">
+      <c r="C1440" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="D1440" s="7" t="s">
+      <c r="D1440" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="E1440" s="7" t="s">
+      <c r="E1440" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F1440" s="7" t="s">
+      <c r="F1440" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="G1440" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1440" s="7" t="s">
+      <c r="G1440" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1440" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="I1440" s="7" t="s">
+      <c r="I1440" s="6" t="s">
         <v>942</v>
       </c>
     </row>
@@ -46014,28 +46047,28 @@
       <c r="A1441" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1441" s="7" t="s">
+      <c r="B1441" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1441" s="7" t="s">
+      <c r="C1441" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="D1441" s="7" t="s">
+      <c r="D1441" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="E1441" s="7" t="s">
+      <c r="E1441" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F1441" s="7" t="s">
+      <c r="F1441" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="G1441" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1441" s="7" t="s">
+      <c r="G1441" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1441" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1441" s="7" t="s">
+      <c r="I1441" s="6" t="s">
         <v>399</v>
       </c>
     </row>
@@ -46043,28 +46076,28 @@
       <c r="A1442" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1442" s="7" t="s">
+      <c r="B1442" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1442" s="7" t="s">
+      <c r="C1442" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="D1442" s="7" t="s">
+      <c r="D1442" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="E1442" s="7" t="s">
+      <c r="E1442" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="F1442" s="7" t="s">
+      <c r="F1442" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="G1442" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1442" s="7" t="s">
+      <c r="G1442" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1442" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1442" s="7" t="s">
+      <c r="I1442" s="6" t="s">
         <v>399</v>
       </c>
     </row>
@@ -46072,28 +46105,28 @@
       <c r="A1443" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1443" s="7" t="s">
+      <c r="B1443" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1443" s="7" t="s">
+      <c r="C1443" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="D1443" s="7" t="s">
+      <c r="D1443" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="E1443" s="7" t="s">
+      <c r="E1443" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F1443" s="7" t="s">
+      <c r="F1443" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="G1443" s="7">
+      <c r="G1443" s="6">
         <v>38</v>
       </c>
-      <c r="H1443" s="7" t="s">
+      <c r="H1443" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1443" s="7" t="s">
+      <c r="I1443" s="6" t="s">
         <v>399</v>
       </c>
     </row>
@@ -46101,28 +46134,28 @@
       <c r="A1444" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1444" s="7" t="s">
+      <c r="B1444" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1444" s="7" t="s">
+      <c r="C1444" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="D1444" s="7" t="s">
+      <c r="D1444" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="E1444" s="7" t="s">
+      <c r="E1444" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F1444" s="7" t="s">
+      <c r="F1444" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="G1444" s="7">
+      <c r="G1444" s="6">
         <v>4</v>
       </c>
-      <c r="H1444" s="7" t="s">
+      <c r="H1444" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="I1444" s="7" t="s">
+      <c r="I1444" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -46130,28 +46163,28 @@
       <c r="A1445" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1445" s="7" t="s">
+      <c r="B1445" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C1445" s="7" t="s">
+      <c r="C1445" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="D1445" s="7" t="s">
+      <c r="D1445" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="E1445" s="7" t="s">
+      <c r="E1445" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F1445" s="7" t="s">
+      <c r="F1445" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="G1445" s="7">
+      <c r="G1445" s="6">
         <v>25</v>
       </c>
-      <c r="H1445" s="7" t="s">
+      <c r="H1445" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="I1445" s="7" t="s">
+      <c r="I1445" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -46159,28 +46192,28 @@
       <c r="A1446" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1446" s="7" t="s">
+      <c r="B1446" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1446" s="7" t="s">
+      <c r="C1446" s="6" t="s">
         <v>950</v>
       </c>
-      <c r="D1446" s="7" t="s">
+      <c r="D1446" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="E1446" s="7" t="s">
+      <c r="E1446" s="6" t="s">
         <v>952</v>
       </c>
-      <c r="F1446" s="7" t="s">
+      <c r="F1446" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="G1446" s="7">
+      <c r="G1446" s="6">
         <v>24</v>
       </c>
-      <c r="H1446" s="7" t="s">
+      <c r="H1446" s="6" t="s">
         <v>954</v>
       </c>
-      <c r="I1446" s="7" t="s">
+      <c r="I1446" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -46188,28 +46221,28 @@
       <c r="A1447" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1447" s="7" t="s">
+      <c r="B1447" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1447" s="7" t="s">
+      <c r="C1447" s="6" t="s">
         <v>950</v>
       </c>
-      <c r="D1447" s="7" t="s">
+      <c r="D1447" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="E1447" s="7" t="s">
+      <c r="E1447" s="6" t="s">
         <v>955</v>
       </c>
-      <c r="F1447" s="7" t="s">
+      <c r="F1447" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="G1447" s="7">
+      <c r="G1447" s="6">
         <v>25</v>
       </c>
-      <c r="H1447" s="7" t="s">
+      <c r="H1447" s="6" t="s">
         <v>954</v>
       </c>
-      <c r="I1447" s="7" t="s">
+      <c r="I1447" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -46217,28 +46250,28 @@
       <c r="A1448" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1448" s="7" t="s">
+      <c r="B1448" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1448" s="7" t="s">
+      <c r="C1448" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1448" s="7" t="s">
+      <c r="D1448" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1448" s="7" t="s">
+      <c r="E1448" s="6" t="s">
         <v>958</v>
       </c>
-      <c r="F1448" s="7" t="s">
+      <c r="F1448" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="G1448" s="7">
+      <c r="G1448" s="6">
         <v>32</v>
       </c>
-      <c r="H1448" s="7" t="s">
+      <c r="H1448" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1448" s="7" t="s">
+      <c r="I1448" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46246,28 +46279,28 @@
       <c r="A1449" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1449" s="7" t="s">
+      <c r="B1449" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1449" s="7" t="s">
+      <c r="C1449" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1449" s="7" t="s">
+      <c r="D1449" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1449" s="7" t="s">
+      <c r="E1449" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="F1449" s="7" t="s">
+      <c r="F1449" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="G1449" s="7">
+      <c r="G1449" s="6">
         <v>33</v>
       </c>
-      <c r="H1449" s="7" t="s">
+      <c r="H1449" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1449" s="7" t="s">
+      <c r="I1449" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46275,28 +46308,28 @@
       <c r="A1450" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1450" s="7" t="s">
+      <c r="B1450" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1450" s="7" t="s">
+      <c r="C1450" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1450" s="7" t="s">
+      <c r="D1450" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1450" s="7" t="s">
+      <c r="E1450" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1450" s="7" t="s">
+      <c r="F1450" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="G1450" s="7">
+      <c r="G1450" s="6">
         <v>33</v>
       </c>
-      <c r="H1450" s="7" t="s">
+      <c r="H1450" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1450" s="7" t="s">
+      <c r="I1450" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -46304,28 +46337,28 @@
       <c r="A1451" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1451" s="7" t="s">
+      <c r="B1451" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1451" s="7" t="s">
+      <c r="C1451" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1451" s="7" t="s">
+      <c r="D1451" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1451" s="7" t="s">
+      <c r="E1451" s="6" t="s">
         <v>963</v>
       </c>
-      <c r="F1451" s="7" t="s">
+      <c r="F1451" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="G1451" s="7">
+      <c r="G1451" s="6">
         <v>34</v>
       </c>
-      <c r="H1451" s="7" t="s">
+      <c r="H1451" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1451" s="7" t="s">
+      <c r="I1451" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -46333,28 +46366,28 @@
       <c r="A1452" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1452" s="7" t="s">
+      <c r="B1452" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1452" s="7" t="s">
+      <c r="C1452" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1452" s="7" t="s">
+      <c r="D1452" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1452" s="7" t="s">
+      <c r="E1452" s="6" t="s">
         <v>965</v>
       </c>
-      <c r="F1452" s="7" t="s">
+      <c r="F1452" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="G1452" s="7">
+      <c r="G1452" s="6">
         <v>32</v>
       </c>
-      <c r="H1452" s="7" t="s">
+      <c r="H1452" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1452" s="7" t="s">
+      <c r="I1452" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -46362,28 +46395,28 @@
       <c r="A1453" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1453" s="7" t="s">
+      <c r="B1453" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1453" s="7" t="s">
+      <c r="C1453" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="D1453" s="7" t="s">
+      <c r="D1453" s="6" t="s">
         <v>957</v>
       </c>
-      <c r="E1453" s="7" t="s">
+      <c r="E1453" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="F1453" s="7" t="s">
+      <c r="F1453" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="G1453" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1453" s="7" t="s">
+      <c r="G1453" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1453" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="I1453" s="7" t="s">
+      <c r="I1453" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -46391,28 +46424,28 @@
       <c r="A1454" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1454" s="7" t="s">
+      <c r="B1454" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1454" s="7" t="s">
+      <c r="C1454" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1454" s="7" t="s">
+      <c r="D1454" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1454" s="7" t="s">
+      <c r="E1454" s="6" t="s">
         <v>969</v>
       </c>
-      <c r="F1454" s="7" t="s">
+      <c r="F1454" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1454" s="7">
+      <c r="G1454" s="6">
         <v>29</v>
       </c>
-      <c r="H1454" s="7" t="s">
+      <c r="H1454" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1454" s="7" t="s">
+      <c r="I1454" s="6" t="s">
         <v>528</v>
       </c>
     </row>
@@ -46420,28 +46453,28 @@
       <c r="A1455" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1455" s="7" t="s">
+      <c r="B1455" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1455" s="7" t="s">
+      <c r="C1455" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1455" s="7" t="s">
+      <c r="D1455" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1455" s="7" t="s">
+      <c r="E1455" s="6" t="s">
         <v>971</v>
       </c>
-      <c r="F1455" s="7" t="s">
+      <c r="F1455" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1455" s="7">
+      <c r="G1455" s="6">
         <v>29</v>
       </c>
-      <c r="H1455" s="7" t="s">
+      <c r="H1455" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1455" s="7" t="s">
+      <c r="I1455" s="6" t="s">
         <v>528</v>
       </c>
     </row>
@@ -46449,28 +46482,28 @@
       <c r="A1456" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1456" s="7" t="s">
+      <c r="B1456" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1456" s="7" t="s">
+      <c r="C1456" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1456" s="7" t="s">
+      <c r="D1456" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1456" s="7" t="s">
+      <c r="E1456" s="6" t="s">
         <v>972</v>
       </c>
-      <c r="F1456" s="7" t="s">
+      <c r="F1456" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1456" s="7">
+      <c r="G1456" s="6">
         <v>33</v>
       </c>
-      <c r="H1456" s="7" t="s">
+      <c r="H1456" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1456" s="7" t="s">
+      <c r="I1456" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -46478,28 +46511,28 @@
       <c r="A1457" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1457" s="7" t="s">
+      <c r="B1457" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1457" s="7" t="s">
+      <c r="C1457" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1457" s="7" t="s">
+      <c r="D1457" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1457" s="7" t="s">
+      <c r="E1457" s="6" t="s">
         <v>973</v>
       </c>
-      <c r="F1457" s="7" t="s">
+      <c r="F1457" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1457" s="7">
+      <c r="G1457" s="6">
         <v>32</v>
       </c>
-      <c r="H1457" s="7" t="s">
+      <c r="H1457" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1457" s="7" t="s">
+      <c r="I1457" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -46507,28 +46540,28 @@
       <c r="A1458" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1458" s="7" t="s">
+      <c r="B1458" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1458" s="7" t="s">
+      <c r="C1458" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1458" s="7" t="s">
+      <c r="D1458" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1458" s="7" t="s">
+      <c r="E1458" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="F1458" s="7" t="s">
+      <c r="F1458" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1458" s="7">
+      <c r="G1458" s="6">
         <v>32</v>
       </c>
-      <c r="H1458" s="7" t="s">
+      <c r="H1458" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1458" s="7" t="s">
+      <c r="I1458" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -46536,28 +46569,28 @@
       <c r="A1459" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1459" s="7" t="s">
+      <c r="B1459" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1459" s="7" t="s">
+      <c r="C1459" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1459" s="7" t="s">
+      <c r="D1459" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1459" s="7" t="s">
+      <c r="E1459" s="6" t="s">
         <v>963</v>
       </c>
-      <c r="F1459" s="7" t="s">
+      <c r="F1459" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1459" s="7">
+      <c r="G1459" s="6">
         <v>2</v>
       </c>
-      <c r="H1459" s="7" t="s">
+      <c r="H1459" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1459" s="7" t="s">
+      <c r="I1459" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -46565,28 +46598,28 @@
       <c r="A1460" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1460" s="7" t="s">
+      <c r="B1460" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1460" s="7" t="s">
+      <c r="C1460" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1460" s="7" t="s">
+      <c r="D1460" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1460" s="7" t="s">
+      <c r="E1460" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="F1460" s="7" t="s">
+      <c r="F1460" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1460" s="7">
+      <c r="G1460" s="6">
         <v>32</v>
       </c>
-      <c r="H1460" s="7" t="s">
+      <c r="H1460" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1460" s="7" t="s">
+      <c r="I1460" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -46594,28 +46627,28 @@
       <c r="A1461" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1461" s="7" t="s">
+      <c r="B1461" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1461" s="7" t="s">
+      <c r="C1461" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1461" s="7" t="s">
+      <c r="D1461" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1461" s="7" t="s">
+      <c r="E1461" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="F1461" s="7" t="s">
+      <c r="F1461" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="G1461" s="7">
+      <c r="G1461" s="6">
         <v>2</v>
       </c>
-      <c r="H1461" s="7" t="s">
+      <c r="H1461" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1461" s="7" t="s">
+      <c r="I1461" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -46623,28 +46656,28 @@
       <c r="A1462" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1462" s="7" t="s">
+      <c r="B1462" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1462" s="7" t="s">
+      <c r="C1462" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1462" s="7" t="s">
+      <c r="D1462" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1462" s="7" t="s">
+      <c r="E1462" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="F1462" s="7" t="s">
+      <c r="F1462" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1462" s="7">
+      <c r="G1462" s="6">
         <v>32</v>
       </c>
-      <c r="H1462" s="7" t="s">
+      <c r="H1462" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1462" s="7" t="s">
+      <c r="I1462" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46652,28 +46685,28 @@
       <c r="A1463" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1463" s="7" t="s">
+      <c r="B1463" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1463" s="7" t="s">
+      <c r="C1463" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1463" s="7" t="s">
+      <c r="D1463" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1463" s="7" t="s">
+      <c r="E1463" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F1463" s="7" t="s">
+      <c r="F1463" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1463" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1463" s="7" t="s">
+      <c r="G1463" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1463" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1463" s="7" t="s">
+      <c r="I1463" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46681,28 +46714,28 @@
       <c r="A1464" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1464" s="7" t="s">
+      <c r="B1464" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1464" s="7" t="s">
+      <c r="C1464" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1464" s="7" t="s">
+      <c r="D1464" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1464" s="7" t="s">
+      <c r="E1464" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F1464" s="7" t="s">
+      <c r="F1464" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1464" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1464" s="7" t="s">
+      <c r="G1464" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1464" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1464" s="7" t="s">
+      <c r="I1464" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46710,28 +46743,28 @@
       <c r="A1465" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1465" s="7" t="s">
+      <c r="B1465" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1465" s="7" t="s">
+      <c r="C1465" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1465" s="7" t="s">
+      <c r="D1465" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1465" s="7" t="s">
+      <c r="E1465" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="F1465" s="7" t="s">
+      <c r="F1465" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1465" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1465" s="7" t="s">
+      <c r="G1465" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1465" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1465" s="7" t="s">
+      <c r="I1465" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46739,28 +46772,28 @@
       <c r="A1466" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1466" s="7" t="s">
+      <c r="B1466" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1466" s="7" t="s">
+      <c r="C1466" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1466" s="7" t="s">
+      <c r="D1466" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1466" s="7" t="s">
+      <c r="E1466" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1466" s="7" t="s">
+      <c r="F1466" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1466" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1466" s="7" t="s">
+      <c r="G1466" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1466" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1466" s="7" t="s">
+      <c r="I1466" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46768,28 +46801,28 @@
       <c r="A1467" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1467" s="7" t="s">
+      <c r="B1467" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1467" s="7" t="s">
+      <c r="C1467" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1467" s="7" t="s">
+      <c r="D1467" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1467" s="7" t="s">
+      <c r="E1467" s="6" t="s">
         <v>978</v>
       </c>
-      <c r="F1467" s="7" t="s">
+      <c r="F1467" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1467" s="7">
+      <c r="G1467" s="6">
         <v>30</v>
       </c>
-      <c r="H1467" s="7" t="s">
+      <c r="H1467" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1467" s="7" t="s">
+      <c r="I1467" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46797,28 +46830,28 @@
       <c r="A1468" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1468" s="7" t="s">
+      <c r="B1468" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1468" s="7" t="s">
+      <c r="C1468" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1468" s="7" t="s">
+      <c r="D1468" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1468" s="7" t="s">
+      <c r="E1468" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="F1468" s="7" t="s">
+      <c r="F1468" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1468" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1468" s="7" t="s">
+      <c r="G1468" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1468" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1468" s="7" t="s">
+      <c r="I1468" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -46826,28 +46859,28 @@
       <c r="A1469" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1469" s="7" t="s">
+      <c r="B1469" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1469" s="7" t="s">
+      <c r="C1469" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1469" s="7" t="s">
+      <c r="D1469" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1469" s="7" t="s">
+      <c r="E1469" s="6" t="s">
         <v>965</v>
       </c>
-      <c r="F1469" s="7" t="s">
+      <c r="F1469" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1469" s="7">
+      <c r="G1469" s="6">
         <v>2</v>
       </c>
-      <c r="H1469" s="7" t="s">
+      <c r="H1469" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1469" s="7" t="s">
+      <c r="I1469" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -46855,28 +46888,28 @@
       <c r="A1470" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1470" s="7" t="s">
+      <c r="B1470" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1470" s="7" t="s">
+      <c r="C1470" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1470" s="7" t="s">
+      <c r="D1470" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1470" s="7" t="s">
+      <c r="E1470" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="F1470" s="7" t="s">
+      <c r="F1470" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1470" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1470" s="7" t="s">
+      <c r="G1470" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1470" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1470" s="7" t="s">
+      <c r="I1470" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -46884,28 +46917,28 @@
       <c r="A1471" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1471" s="7" t="s">
+      <c r="B1471" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1471" s="7" t="s">
+      <c r="C1471" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1471" s="7" t="s">
+      <c r="D1471" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1471" s="7" t="s">
+      <c r="E1471" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1471" s="7" t="s">
+      <c r="F1471" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1471" s="7">
+      <c r="G1471" s="6">
         <v>2</v>
       </c>
-      <c r="H1471" s="7" t="s">
+      <c r="H1471" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1471" s="7" t="s">
+      <c r="I1471" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -46913,28 +46946,28 @@
       <c r="A1472" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1472" s="7" t="s">
+      <c r="B1472" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1472" s="7" t="s">
+      <c r="C1472" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1472" s="7" t="s">
+      <c r="D1472" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1472" s="7" t="s">
+      <c r="E1472" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="F1472" s="7" t="s">
+      <c r="F1472" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1472" s="7">
+      <c r="G1472" s="6">
         <v>33</v>
       </c>
-      <c r="H1472" s="7" t="s">
+      <c r="H1472" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1472" s="7" t="s">
+      <c r="I1472" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -46942,28 +46975,28 @@
       <c r="A1473" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1473" s="7" t="s">
+      <c r="B1473" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1473" s="7" t="s">
+      <c r="C1473" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1473" s="7" t="s">
+      <c r="D1473" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1473" s="7" t="s">
+      <c r="E1473" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="F1473" s="7" t="s">
+      <c r="F1473" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1473" s="7">
+      <c r="G1473" s="6">
         <v>2</v>
       </c>
-      <c r="H1473" s="7" t="s">
+      <c r="H1473" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1473" s="7" t="s">
+      <c r="I1473" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -46971,28 +47004,28 @@
       <c r="A1474" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1474" s="7" t="s">
+      <c r="B1474" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1474" s="7" t="s">
+      <c r="C1474" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D1474" s="7" t="s">
+      <c r="D1474" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="E1474" s="7" t="s">
+      <c r="E1474" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="F1474" s="7" t="s">
+      <c r="F1474" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="G1474" s="7">
+      <c r="G1474" s="6">
         <v>31</v>
       </c>
-      <c r="H1474" s="7" t="s">
+      <c r="H1474" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1474" s="7" t="s">
+      <c r="I1474" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47000,28 +47033,28 @@
       <c r="A1475" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1475" s="7" t="s">
+      <c r="B1475" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1475" s="7" t="s">
+      <c r="C1475" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1475" s="7" t="s">
+      <c r="D1475" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1475" s="7" t="s">
+      <c r="E1475" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1475" s="7" t="s">
+      <c r="F1475" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1475" s="7">
+      <c r="G1475" s="6">
         <v>33</v>
       </c>
-      <c r="H1475" s="7" t="s">
+      <c r="H1475" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1475" s="7" t="s">
+      <c r="I1475" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -47029,28 +47062,28 @@
       <c r="A1476" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1476" s="7" t="s">
+      <c r="B1476" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1476" s="7" t="s">
+      <c r="C1476" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1476" s="7" t="s">
+      <c r="D1476" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1476" s="7" t="s">
+      <c r="E1476" s="6" t="s">
         <v>958</v>
       </c>
-      <c r="F1476" s="7" t="s">
+      <c r="F1476" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1476" s="7">
+      <c r="G1476" s="6">
         <v>32</v>
       </c>
-      <c r="H1476" s="7" t="s">
+      <c r="H1476" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1476" s="7" t="s">
+      <c r="I1476" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -47058,28 +47091,28 @@
       <c r="A1477" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1477" s="7" t="s">
+      <c r="B1477" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1477" s="7" t="s">
+      <c r="C1477" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1477" s="7" t="s">
+      <c r="D1477" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1477" s="7" t="s">
+      <c r="E1477" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="F1477" s="7" t="s">
+      <c r="F1477" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1477" s="7">
+      <c r="G1477" s="6">
         <v>33</v>
       </c>
-      <c r="H1477" s="7" t="s">
+      <c r="H1477" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1477" s="7" t="s">
+      <c r="I1477" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -47087,28 +47120,28 @@
       <c r="A1478" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1478" s="7" t="s">
+      <c r="B1478" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1478" s="7" t="s">
+      <c r="C1478" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1478" s="7" t="s">
+      <c r="D1478" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1478" s="7" t="s">
+      <c r="E1478" s="6" t="s">
         <v>965</v>
       </c>
-      <c r="F1478" s="7" t="s">
+      <c r="F1478" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1478" s="7">
+      <c r="G1478" s="6">
         <v>33</v>
       </c>
-      <c r="H1478" s="7" t="s">
+      <c r="H1478" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1478" s="7" t="s">
+      <c r="I1478" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47116,28 +47149,28 @@
       <c r="A1479" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1479" s="7" t="s">
+      <c r="B1479" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1479" s="7" t="s">
+      <c r="C1479" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1479" s="7" t="s">
+      <c r="D1479" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1479" s="7" t="s">
+      <c r="E1479" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="F1479" s="7" t="s">
+      <c r="F1479" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1479" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1479" s="7" t="s">
+      <c r="G1479" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1479" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1479" s="7" t="s">
+      <c r="I1479" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47145,28 +47178,28 @@
       <c r="A1480" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1480" s="7" t="s">
+      <c r="B1480" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1480" s="7" t="s">
+      <c r="C1480" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="D1480" s="7" t="s">
+      <c r="D1480" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="E1480" s="7" t="s">
+      <c r="E1480" s="6" t="s">
         <v>963</v>
       </c>
-      <c r="F1480" s="7" t="s">
+      <c r="F1480" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="G1480" s="7">
+      <c r="G1480" s="6">
         <v>34</v>
       </c>
-      <c r="H1480" s="7" t="s">
+      <c r="H1480" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I1480" s="7" t="s">
+      <c r="I1480" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47174,28 +47207,28 @@
       <c r="A1481" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1481" s="7" t="s">
+      <c r="B1481" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1481" s="7" t="s">
+      <c r="C1481" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1481" s="7" t="s">
+      <c r="D1481" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1481" s="7" t="s">
+      <c r="E1481" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="F1481" s="7" t="s">
+      <c r="F1481" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1481" s="7">
+      <c r="G1481" s="6">
         <v>33</v>
       </c>
-      <c r="H1481" s="7" t="s">
+      <c r="H1481" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1481" s="7" t="s">
+      <c r="I1481" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -47203,28 +47236,28 @@
       <c r="A1482" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1482" s="7" t="s">
+      <c r="B1482" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1482" s="7" t="s">
+      <c r="C1482" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1482" s="7" t="s">
+      <c r="D1482" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1482" s="7" t="s">
+      <c r="E1482" s="6" t="s">
         <v>989</v>
       </c>
-      <c r="F1482" s="7" t="s">
+      <c r="F1482" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1482" s="7">
+      <c r="G1482" s="6">
         <v>33</v>
       </c>
-      <c r="H1482" s="7" t="s">
+      <c r="H1482" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1482" s="7" t="s">
+      <c r="I1482" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -47232,28 +47265,28 @@
       <c r="A1483" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1483" s="7" t="s">
+      <c r="B1483" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1483" s="7" t="s">
+      <c r="C1483" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1483" s="7" t="s">
+      <c r="D1483" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1483" s="7" t="s">
+      <c r="E1483" s="6" t="s">
         <v>990</v>
       </c>
-      <c r="F1483" s="7" t="s">
+      <c r="F1483" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="G1483" s="7">
+      <c r="G1483" s="6">
         <v>33</v>
       </c>
-      <c r="H1483" s="7" t="s">
+      <c r="H1483" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1483" s="7" t="s">
+      <c r="I1483" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -47261,28 +47294,28 @@
       <c r="A1484" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1484" s="7" t="s">
+      <c r="B1484" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1484" s="7" t="s">
+      <c r="C1484" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1484" s="7" t="s">
+      <c r="D1484" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1484" s="7" t="s">
+      <c r="E1484" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="F1484" s="7" t="s">
+      <c r="F1484" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1484" s="7">
+      <c r="G1484" s="6">
         <v>33</v>
       </c>
-      <c r="H1484" s="7" t="s">
+      <c r="H1484" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1484" s="7" t="s">
+      <c r="I1484" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -47290,28 +47323,28 @@
       <c r="A1485" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1485" s="7" t="s">
+      <c r="B1485" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1485" s="7" t="s">
+      <c r="C1485" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1485" s="7" t="s">
+      <c r="D1485" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1485" s="7" t="s">
+      <c r="E1485" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F1485" s="7" t="s">
+      <c r="F1485" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1485" s="7">
+      <c r="G1485" s="6">
         <v>34</v>
       </c>
-      <c r="H1485" s="7" t="s">
+      <c r="H1485" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1485" s="7" t="s">
+      <c r="I1485" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -47319,28 +47352,28 @@
       <c r="A1486" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1486" s="7" t="s">
+      <c r="B1486" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1486" s="7" t="s">
+      <c r="C1486" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1486" s="7" t="s">
+      <c r="D1486" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1486" s="7" t="s">
+      <c r="E1486" s="6" t="s">
         <v>993</v>
       </c>
-      <c r="F1486" s="7" t="s">
+      <c r="F1486" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1486" s="7">
+      <c r="G1486" s="6">
         <v>34</v>
       </c>
-      <c r="H1486" s="7" t="s">
+      <c r="H1486" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1486" s="7" t="s">
+      <c r="I1486" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47348,28 +47381,28 @@
       <c r="A1487" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1487" s="7" t="s">
+      <c r="B1487" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1487" s="7" t="s">
+      <c r="C1487" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1487" s="7" t="s">
+      <c r="D1487" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1487" s="7" t="s">
+      <c r="E1487" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="F1487" s="7" t="s">
+      <c r="F1487" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="G1487" s="7">
+      <c r="G1487" s="6">
         <v>33</v>
       </c>
-      <c r="H1487" s="7" t="s">
+      <c r="H1487" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1487" s="7" t="s">
+      <c r="I1487" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47377,28 +47410,28 @@
       <c r="A1488" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1488" s="7" t="s">
+      <c r="B1488" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1488" s="7" t="s">
+      <c r="C1488" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1488" s="7" t="s">
+      <c r="D1488" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1488" s="7" t="s">
+      <c r="E1488" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="F1488" s="7" t="s">
+      <c r="F1488" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="G1488" s="7">
+      <c r="G1488" s="6">
         <v>31</v>
       </c>
-      <c r="H1488" s="7" t="s">
+      <c r="H1488" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1488" s="7" t="s">
+      <c r="I1488" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -47406,28 +47439,28 @@
       <c r="A1489" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1489" s="7" t="s">
+      <c r="B1489" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1489" s="7" t="s">
+      <c r="C1489" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1489" s="7" t="s">
+      <c r="D1489" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1489" s="7" t="s">
+      <c r="E1489" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="F1489" s="7" t="s">
+      <c r="F1489" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="G1489" s="7">
+      <c r="G1489" s="6">
         <v>31</v>
       </c>
-      <c r="H1489" s="7" t="s">
+      <c r="H1489" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1489" s="7" t="s">
+      <c r="I1489" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -47435,28 +47468,28 @@
       <c r="A1490" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1490" s="7" t="s">
+      <c r="B1490" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1490" s="7" t="s">
+      <c r="C1490" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="D1490" s="7" t="s">
+      <c r="D1490" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="E1490" s="7" t="s">
+      <c r="E1490" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F1490" s="7" t="s">
+      <c r="F1490" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="G1490" s="7">
+      <c r="G1490" s="6">
         <v>33</v>
       </c>
-      <c r="H1490" s="7" t="s">
+      <c r="H1490" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I1490" s="7" t="s">
+      <c r="I1490" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -47464,28 +47497,28 @@
       <c r="A1491" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1491" s="7" t="s">
+      <c r="B1491" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1491" s="7" t="s">
+      <c r="C1491" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1491" s="7" t="s">
+      <c r="D1491" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1491" s="7" t="s">
+      <c r="E1491" s="6" t="s">
         <v>999</v>
       </c>
-      <c r="F1491" s="7" t="s">
+      <c r="F1491" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1491" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1491" s="7" t="s">
+      <c r="G1491" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1491" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1491" s="7" t="s">
+      <c r="I1491" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47493,28 +47526,28 @@
       <c r="A1492" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1492" s="7" t="s">
+      <c r="B1492" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1492" s="7" t="s">
+      <c r="C1492" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1492" s="7" t="s">
+      <c r="D1492" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1492" s="7" t="s">
+      <c r="E1492" s="6" t="s">
         <v>963</v>
       </c>
-      <c r="F1492" s="7" t="s">
+      <c r="F1492" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1492" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1492" s="7" t="s">
+      <c r="G1492" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1492" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1492" s="7" t="s">
+      <c r="I1492" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47522,28 +47555,28 @@
       <c r="A1493" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1493" s="7" t="s">
+      <c r="B1493" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1493" s="7" t="s">
+      <c r="C1493" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1493" s="7" t="s">
+      <c r="D1493" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1493" s="7" t="s">
+      <c r="E1493" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="F1493" s="7" t="s">
+      <c r="F1493" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1493" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1493" s="7" t="s">
+      <c r="G1493" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1493" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1493" s="7" t="s">
+      <c r="I1493" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47551,28 +47584,28 @@
       <c r="A1494" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1494" s="7" t="s">
+      <c r="B1494" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1494" s="7" t="s">
+      <c r="C1494" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1494" s="7" t="s">
+      <c r="D1494" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1494" s="7" t="s">
+      <c r="E1494" s="6" t="s">
         <v>993</v>
       </c>
-      <c r="F1494" s="7" t="s">
+      <c r="F1494" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1494" s="7">
+      <c r="G1494" s="6">
         <v>34</v>
       </c>
-      <c r="H1494" s="7" t="s">
+      <c r="H1494" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1494" s="7" t="s">
+      <c r="I1494" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47580,28 +47613,28 @@
       <c r="A1495" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1495" s="7" t="s">
+      <c r="B1495" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1495" s="7" t="s">
+      <c r="C1495" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1495" s="7" t="s">
+      <c r="D1495" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1495" s="7" t="s">
+      <c r="E1495" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="F1495" s="7" t="s">
+      <c r="F1495" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1495" s="7">
+      <c r="G1495" s="6">
         <v>33</v>
       </c>
-      <c r="H1495" s="7" t="s">
+      <c r="H1495" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1495" s="7" t="s">
+      <c r="I1495" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47609,28 +47642,28 @@
       <c r="A1496" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1496" s="7" t="s">
+      <c r="B1496" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1496" s="7" t="s">
+      <c r="C1496" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1496" s="7" t="s">
+      <c r="D1496" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1496" s="7" t="s">
+      <c r="E1496" s="6" t="s">
         <v>1001</v>
       </c>
-      <c r="F1496" s="7" t="s">
+      <c r="F1496" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1496" s="7">
+      <c r="G1496" s="6">
         <v>2</v>
       </c>
-      <c r="H1496" s="7" t="s">
+      <c r="H1496" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1496" s="7" t="s">
+      <c r="I1496" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -47638,28 +47671,28 @@
       <c r="A1497" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1497" s="7" t="s">
+      <c r="B1497" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1497" s="7" t="s">
+      <c r="C1497" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1497" s="7" t="s">
+      <c r="D1497" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1497" s="7" t="s">
+      <c r="E1497" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="F1497" s="7" t="s">
+      <c r="F1497" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1497" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1497" s="7" t="s">
+      <c r="G1497" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1497" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1497" s="7" t="s">
+      <c r="I1497" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47667,28 +47700,28 @@
       <c r="A1498" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1498" s="7" t="s">
+      <c r="B1498" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1498" s="7" t="s">
+      <c r="C1498" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1498" s="7" t="s">
+      <c r="D1498" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1498" s="7" t="s">
+      <c r="E1498" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="F1498" s="7" t="s">
+      <c r="F1498" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1498" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1498" s="7" t="s">
+      <c r="G1498" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1498" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1498" s="7" t="s">
+      <c r="I1498" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47696,28 +47729,28 @@
       <c r="A1499" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1499" s="7" t="s">
+      <c r="B1499" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1499" s="7" t="s">
+      <c r="C1499" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1499" s="7" t="s">
+      <c r="D1499" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1499" s="7" t="s">
+      <c r="E1499" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="F1499" s="7" t="s">
+      <c r="F1499" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1499" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1499" s="7" t="s">
+      <c r="G1499" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1499" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1499" s="7" t="s">
+      <c r="I1499" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47725,28 +47758,28 @@
       <c r="A1500" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1500" s="7" t="s">
+      <c r="B1500" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1500" s="7" t="s">
+      <c r="C1500" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1500" s="7" t="s">
+      <c r="D1500" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1500" s="7" t="s">
+      <c r="E1500" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="F1500" s="7" t="s">
+      <c r="F1500" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1500" s="7">
+      <c r="G1500" s="6">
         <v>3</v>
       </c>
-      <c r="H1500" s="7" t="s">
+      <c r="H1500" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1500" s="7" t="s">
+      <c r="I1500" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47754,28 +47787,28 @@
       <c r="A1501" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1501" s="7" t="s">
+      <c r="B1501" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1501" s="7" t="s">
+      <c r="C1501" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1501" s="7" t="s">
+      <c r="D1501" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1501" s="7" t="s">
+      <c r="E1501" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F1501" s="7" t="s">
+      <c r="F1501" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1501" s="7">
+      <c r="G1501" s="6">
         <v>34</v>
       </c>
-      <c r="H1501" s="7" t="s">
+      <c r="H1501" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1501" s="7" t="s">
+      <c r="I1501" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47783,28 +47816,28 @@
       <c r="A1502" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1502" s="7" t="s">
+      <c r="B1502" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1502" s="7" t="s">
+      <c r="C1502" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1502" s="7" t="s">
+      <c r="D1502" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1502" s="7" t="s">
+      <c r="E1502" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="F1502" s="7" t="s">
+      <c r="F1502" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1502" s="7">
+      <c r="G1502" s="6">
         <v>2</v>
       </c>
-      <c r="H1502" s="7" t="s">
+      <c r="H1502" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1502" s="7" t="s">
+      <c r="I1502" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47812,28 +47845,28 @@
       <c r="A1503" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1503" s="7" t="s">
+      <c r="B1503" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1503" s="7" t="s">
+      <c r="C1503" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1503" s="7" t="s">
+      <c r="D1503" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1503" s="7" t="s">
+      <c r="E1503" s="6" t="s">
         <v>978</v>
       </c>
-      <c r="F1503" s="7" t="s">
+      <c r="F1503" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1503" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1503" s="7" t="s">
+      <c r="G1503" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1503" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1503" s="7" t="s">
+      <c r="I1503" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47841,28 +47874,28 @@
       <c r="A1504" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1504" s="7" t="s">
+      <c r="B1504" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1504" s="7" t="s">
+      <c r="C1504" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1504" s="7" t="s">
+      <c r="D1504" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1504" s="7" t="s">
+      <c r="E1504" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="F1504" s="7" t="s">
+      <c r="F1504" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1504" s="7">
+      <c r="G1504" s="6">
         <v>33</v>
       </c>
-      <c r="H1504" s="7" t="s">
+      <c r="H1504" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1504" s="7" t="s">
+      <c r="I1504" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47870,28 +47903,28 @@
       <c r="A1505" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1505" s="7" t="s">
+      <c r="B1505" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1505" s="7" t="s">
+      <c r="C1505" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1505" s="7" t="s">
+      <c r="D1505" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1505" s="7" t="s">
+      <c r="E1505" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="F1505" s="7" t="s">
+      <c r="F1505" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1505" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1505" s="7" t="s">
+      <c r="G1505" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1505" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1505" s="7" t="s">
+      <c r="I1505" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -47899,28 +47932,28 @@
       <c r="A1506" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1506" s="7" t="s">
+      <c r="B1506" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1506" s="7" t="s">
+      <c r="C1506" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1506" s="7" t="s">
+      <c r="D1506" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1506" s="7" t="s">
+      <c r="E1506" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="F1506" s="7" t="s">
+      <c r="F1506" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1506" s="7">
+      <c r="G1506" s="6">
         <v>2</v>
       </c>
-      <c r="H1506" s="7" t="s">
+      <c r="H1506" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1506" s="7" t="s">
+      <c r="I1506" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -47928,28 +47961,28 @@
       <c r="A1507" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1507" s="7" t="s">
+      <c r="B1507" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1507" s="7" t="s">
+      <c r="C1507" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1507" s="7" t="s">
+      <c r="D1507" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1507" s="7" t="s">
+      <c r="E1507" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="F1507" s="7" t="s">
+      <c r="F1507" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1507" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1507" s="7" t="s">
+      <c r="G1507" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1507" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1507" s="7" t="s">
+      <c r="I1507" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -47957,28 +47990,28 @@
       <c r="A1508" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1508" s="7" t="s">
+      <c r="B1508" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1508" s="7" t="s">
+      <c r="C1508" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1508" s="7" t="s">
+      <c r="D1508" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1508" s="7" t="s">
+      <c r="E1508" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1508" s="7" t="s">
+      <c r="F1508" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1508" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1508" s="7" t="s">
+      <c r="G1508" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1508" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1508" s="7" t="s">
+      <c r="I1508" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -47986,28 +48019,28 @@
       <c r="A1509" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1509" s="7" t="s">
+      <c r="B1509" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1509" s="7" t="s">
+      <c r="C1509" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1509" s="7" t="s">
+      <c r="D1509" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1509" s="7" t="s">
+      <c r="E1509" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="F1509" s="7" t="s">
+      <c r="F1509" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1509" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1509" s="7" t="s">
+      <c r="G1509" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1509" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1509" s="7" t="s">
+      <c r="I1509" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48015,28 +48048,28 @@
       <c r="A1510" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1510" s="7" t="s">
+      <c r="B1510" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1510" s="7" t="s">
+      <c r="C1510" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1510" s="7" t="s">
+      <c r="D1510" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1510" s="7" t="s">
+      <c r="E1510" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="F1510" s="7" t="s">
+      <c r="F1510" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1510" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1510" s="7" t="s">
+      <c r="G1510" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1510" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1510" s="7" t="s">
+      <c r="I1510" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48044,28 +48077,28 @@
       <c r="A1511" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1511" s="7" t="s">
+      <c r="B1511" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1511" s="7" t="s">
+      <c r="C1511" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1511" s="7" t="s">
+      <c r="D1511" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1511" s="7" t="s">
+      <c r="E1511" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="F1511" s="7" t="s">
+      <c r="F1511" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1511" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1511" s="7" t="s">
+      <c r="G1511" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1511" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1511" s="7" t="s">
+      <c r="I1511" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48073,28 +48106,28 @@
       <c r="A1512" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1512" s="7" t="s">
+      <c r="B1512" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1512" s="7" t="s">
+      <c r="C1512" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1512" s="7" t="s">
+      <c r="D1512" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1512" s="7" t="s">
+      <c r="E1512" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="F1512" s="7" t="s">
+      <c r="F1512" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1512" s="7">
+      <c r="G1512" s="6">
         <v>33</v>
       </c>
-      <c r="H1512" s="7" t="s">
+      <c r="H1512" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1512" s="7" t="s">
+      <c r="I1512" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48102,28 +48135,28 @@
       <c r="A1513" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1513" s="7" t="s">
+      <c r="B1513" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1513" s="7" t="s">
+      <c r="C1513" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1513" s="7" t="s">
+      <c r="D1513" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1513" s="7" t="s">
+      <c r="E1513" s="6" t="s">
         <v>989</v>
       </c>
-      <c r="F1513" s="7" t="s">
+      <c r="F1513" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="G1513" s="7">
+      <c r="G1513" s="6">
         <v>33</v>
       </c>
-      <c r="H1513" s="7" t="s">
+      <c r="H1513" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1513" s="7" t="s">
+      <c r="I1513" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48131,28 +48164,28 @@
       <c r="A1514" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1514" s="7" t="s">
+      <c r="B1514" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1514" s="7" t="s">
+      <c r="C1514" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1514" s="7" t="s">
+      <c r="D1514" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1514" s="7" t="s">
+      <c r="E1514" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="F1514" s="7" t="s">
+      <c r="F1514" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1514" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1514" s="7" t="s">
+      <c r="G1514" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1514" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1514" s="7" t="s">
+      <c r="I1514" s="6" t="s">
         <v>100</v>
       </c>
     </row>
@@ -48160,28 +48193,28 @@
       <c r="A1515" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1515" s="7" t="s">
+      <c r="B1515" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1515" s="7" t="s">
+      <c r="C1515" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1515" s="7" t="s">
+      <c r="D1515" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1515" s="7" t="s">
+      <c r="E1515" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F1515" s="7" t="s">
+      <c r="F1515" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1515" s="7">
+      <c r="G1515" s="6">
         <v>33</v>
       </c>
-      <c r="H1515" s="7" t="s">
+      <c r="H1515" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1515" s="7" t="s">
+      <c r="I1515" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -48189,28 +48222,28 @@
       <c r="A1516" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1516" s="7" t="s">
+      <c r="B1516" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1516" s="7" t="s">
+      <c r="C1516" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1516" s="7" t="s">
+      <c r="D1516" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1516" s="7" t="s">
+      <c r="E1516" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="F1516" s="7" t="s">
+      <c r="F1516" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1516" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1516" s="7" t="s">
+      <c r="G1516" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1516" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1516" s="7" t="s">
+      <c r="I1516" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -48218,28 +48251,28 @@
       <c r="A1517" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1517" s="7" t="s">
+      <c r="B1517" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1517" s="7" t="s">
+      <c r="C1517" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1517" s="7" t="s">
+      <c r="D1517" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1517" s="7" t="s">
+      <c r="E1517" s="6" t="s">
         <v>990</v>
       </c>
-      <c r="F1517" s="7" t="s">
+      <c r="F1517" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1517" s="7">
+      <c r="G1517" s="6">
         <v>33</v>
       </c>
-      <c r="H1517" s="7" t="s">
+      <c r="H1517" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1517" s="7" t="s">
+      <c r="I1517" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -48247,28 +48280,28 @@
       <c r="A1518" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1518" s="7" t="s">
+      <c r="B1518" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1518" s="7" t="s">
+      <c r="C1518" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1518" s="7" t="s">
+      <c r="D1518" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1518" s="7" t="s">
+      <c r="E1518" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="F1518" s="7" t="s">
+      <c r="F1518" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1518" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1518" s="7" t="s">
+      <c r="G1518" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1518" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1518" s="7" t="s">
+      <c r="I1518" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -48276,28 +48309,28 @@
       <c r="A1519" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1519" s="7" t="s">
+      <c r="B1519" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1519" s="7" t="s">
+      <c r="C1519" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1519" s="7" t="s">
+      <c r="D1519" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1519" s="7" t="s">
+      <c r="E1519" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="F1519" s="7" t="s">
+      <c r="F1519" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1519" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1519" s="7" t="s">
+      <c r="G1519" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1519" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1519" s="7" t="s">
+      <c r="I1519" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -48305,28 +48338,28 @@
       <c r="A1520" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1520" s="7" t="s">
+      <c r="B1520" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1520" s="7" t="s">
+      <c r="C1520" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1520" s="7" t="s">
+      <c r="D1520" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1520" s="7" t="s">
+      <c r="E1520" s="6" t="s">
         <v>972</v>
       </c>
-      <c r="F1520" s="7" t="s">
+      <c r="F1520" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1520" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1520" s="7" t="s">
+      <c r="G1520" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1520" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1520" s="7" t="s">
+      <c r="I1520" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -48334,28 +48367,28 @@
       <c r="A1521" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1521" s="7" t="s">
+      <c r="B1521" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1521" s="7" t="s">
+      <c r="C1521" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1521" s="7" t="s">
+      <c r="D1521" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1521" s="7" t="s">
+      <c r="E1521" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="F1521" s="7" t="s">
+      <c r="F1521" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1521" s="7">
+      <c r="G1521" s="6">
         <v>31</v>
       </c>
-      <c r="H1521" s="7" t="s">
+      <c r="H1521" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1521" s="7" t="s">
+      <c r="I1521" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -48363,29 +48396,928 @@
       <c r="A1522" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1522" s="7" t="s">
+      <c r="B1522" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C1522" s="7" t="s">
+      <c r="C1522" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="D1522" s="7" t="s">
+      <c r="D1522" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="E1522" s="7" t="s">
+      <c r="E1522" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="F1522" s="7" t="s">
+      <c r="F1522" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="G1522" s="7">
+      <c r="G1522" s="6">
         <v>31</v>
       </c>
-      <c r="H1522" s="7" t="s">
+      <c r="H1522" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I1522" s="7" t="s">
+      <c r="I1522" s="6" t="s">
         <v>516</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:9">
+      <c r="A1523" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1523" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1523" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D1523" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E1523" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1523" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G1523" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1523" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1523" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:9">
+      <c r="A1524" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1524" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1524" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D1524" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E1524" s="7" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F1524" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G1524" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1524" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1524" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:9">
+      <c r="A1525" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1525" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1525" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D1525" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E1525" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F1525" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G1525" s="7">
+        <v>21</v>
+      </c>
+      <c r="H1525" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1525" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:9">
+      <c r="A1526" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1526" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1526" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1526" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1526" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1526" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1526" s="7">
+        <v>34</v>
+      </c>
+      <c r="H1526" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1526" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:9">
+      <c r="A1527" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1527" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1527" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1527" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1527" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1527" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1527" s="7">
+        <v>34</v>
+      </c>
+      <c r="H1527" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1527" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:9">
+      <c r="A1528" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1528" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1528" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1528" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1528" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1528" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1528" s="7">
+        <v>36</v>
+      </c>
+      <c r="H1528" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1528" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:9">
+      <c r="A1529" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1529" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1529" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1529" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1529" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1529" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1529" s="7">
+        <v>35</v>
+      </c>
+      <c r="H1529" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1529" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:9">
+      <c r="A1530" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1530" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1530" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1530" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1530" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1530" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1530" s="7">
+        <v>35</v>
+      </c>
+      <c r="H1530" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1530" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:9">
+      <c r="A1531" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1531" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1531" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1531" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1531" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F1531" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1531" s="7">
+        <v>32</v>
+      </c>
+      <c r="H1531" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1531" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:9">
+      <c r="A1532" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1532" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1532" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1532" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1532" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1532" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1532" s="7">
+        <v>36</v>
+      </c>
+      <c r="H1532" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1532" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:9">
+      <c r="A1533" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1533" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1533" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1533" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1533" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F1533" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1533" s="7">
+        <v>34</v>
+      </c>
+      <c r="H1533" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1533" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:9">
+      <c r="A1534" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1534" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1534" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1534" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1534" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1534" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1534" s="7">
+        <v>31</v>
+      </c>
+      <c r="H1534" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1534" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:9">
+      <c r="A1535" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1535" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1535" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1535" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1535" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1535" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G1535" s="7">
+        <v>34</v>
+      </c>
+      <c r="H1535" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1535" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:9">
+      <c r="A1536" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1536" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1536" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1536" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1536" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1536" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G1536" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1536" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1536" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:9">
+      <c r="A1537" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1537" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1537" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1537" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1537" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1537" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G1537" s="7">
+        <v>29</v>
+      </c>
+      <c r="H1537" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1537" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:9">
+      <c r="A1538" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1538" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1538" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1538" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1538" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1538" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G1538" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1538" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1538" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:9">
+      <c r="A1539" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1539" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1539" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1539" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1539" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F1539" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G1539" s="7">
+        <v>2</v>
+      </c>
+      <c r="H1539" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1539" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:9">
+      <c r="A1540" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1540" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1540" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1540" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1540" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1540" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G1540" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1540" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1540" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:9">
+      <c r="A1541" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1541" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1541" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1541" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1541" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1541" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G1541" s="7">
+        <v>26</v>
+      </c>
+      <c r="H1541" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1541" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:9">
+      <c r="A1542" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1542" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1542" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1542" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1542" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1542" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G1542" s="7">
+        <v>31</v>
+      </c>
+      <c r="H1542" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1542" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:9">
+      <c r="A1543" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1543" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1543" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1543" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1543" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1543" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1543" s="7">
+        <v>31</v>
+      </c>
+      <c r="H1543" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1543" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:9">
+      <c r="A1544" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1544" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1544" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1544" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1544" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1544" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1544" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1544" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1544" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:9">
+      <c r="A1545" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1545" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1545" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1545" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1545" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F1545" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1545" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1545" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1545" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:9">
+      <c r="A1546" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1546" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1546" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1546" s="7" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E1546" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1546" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1546" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1546" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1546" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:9">
+      <c r="A1547" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1547" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1547" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1547" s="7" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E1547" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1547" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1547" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1547" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1547" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:9">
+      <c r="A1548" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1548" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1548" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1548" s="7" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E1548" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1548" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1548" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1548" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1548" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:9">
+      <c r="A1549" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1549" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1549" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1549" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1549" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1549" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1549" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1549" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1549" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:9">
+      <c r="A1550" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1550" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1550" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1550" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1550" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F1550" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1550" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1550" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1550" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:9">
+      <c r="A1551" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1551" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1551" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1551" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1551" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1551" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1551" s="7">
+        <v>36</v>
+      </c>
+      <c r="H1551" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1551" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:9">
+      <c r="A1552" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1552" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1552" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1552" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1552" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1552" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1552" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1552" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1552" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:9">
+      <c r="A1553" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1553" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1553" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1553" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E1553" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1553" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1553" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1553" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1553" s="7" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12425" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13281" uniqueCount="1167">
   <si>
     <t>校区</t>
   </si>
@@ -3081,6 +3081,456 @@
   </si>
   <si>
     <t>OpticalFiberCommunicationSystem(全英文授课）</t>
+  </si>
+  <si>
+    <t>教育科学与技术学院</t>
+  </si>
+  <si>
+    <t>JK1104C1S</t>
+  </si>
+  <si>
+    <t>学习科学与技术(双语)</t>
+  </si>
+  <si>
+    <t>B231701</t>
+  </si>
+  <si>
+    <t>刘永贵</t>
+  </si>
+  <si>
+    <t>B231702</t>
+  </si>
+  <si>
+    <t>JK1109C1S</t>
+  </si>
+  <si>
+    <t>人工智能与教育应用</t>
+  </si>
+  <si>
+    <t>陆凯莉</t>
+  </si>
+  <si>
+    <t>第17周周6(2026-06-27) 07:50-09:40</t>
+  </si>
+  <si>
+    <t>B251701</t>
+  </si>
+  <si>
+    <t>JK1112C1S</t>
+  </si>
+  <si>
+    <t>教育统计与测量</t>
+  </si>
+  <si>
+    <t>B241601</t>
+  </si>
+  <si>
+    <t>上官晨雨</t>
+  </si>
+  <si>
+    <t>JK1118C1S</t>
+  </si>
+  <si>
+    <t>教育技术研究方法</t>
+  </si>
+  <si>
+    <t>唐湘宁/陈华若</t>
+  </si>
+  <si>
+    <t>JK1119C1S</t>
+  </si>
+  <si>
+    <t>情感计算</t>
+  </si>
+  <si>
+    <t>单俊豪</t>
+  </si>
+  <si>
+    <t>第18周周2(2026-06-30) 07:50-09:40</t>
+  </si>
+  <si>
+    <t>JK1121C1S</t>
+  </si>
+  <si>
+    <t>深度学习</t>
+  </si>
+  <si>
+    <t>程薇/姜玻</t>
+  </si>
+  <si>
+    <t>JK1205C1S</t>
+  </si>
+  <si>
+    <t>数据结构（混合式）</t>
+  </si>
+  <si>
+    <t>宋婉茹/王心怡</t>
+  </si>
+  <si>
+    <t>JK1213C1S</t>
+  </si>
+  <si>
+    <t>JK1305C1S</t>
+  </si>
+  <si>
+    <t>教学技术与媒体(混合式）</t>
+  </si>
+  <si>
+    <t>肖婉</t>
+  </si>
+  <si>
+    <t>锁金</t>
+  </si>
+  <si>
+    <t>WY1006YKS</t>
+  </si>
+  <si>
+    <t>英语II</t>
+  </si>
+  <si>
+    <t>Y250001</t>
+  </si>
+  <si>
+    <t>卞树荣</t>
+  </si>
+  <si>
+    <t>第16周周2(2026-06-16) 07:50-09:40</t>
+  </si>
+  <si>
+    <t>锁金－305</t>
+  </si>
+  <si>
+    <t>材料科学与工程学院</t>
+  </si>
+  <si>
+    <t>CL1266JCS</t>
+  </si>
+  <si>
+    <t>太阳能电池材料及技术</t>
+  </si>
+  <si>
+    <t>B230307</t>
+  </si>
+  <si>
+    <t>夏俊民</t>
+  </si>
+  <si>
+    <t>B230309</t>
+  </si>
+  <si>
+    <t>B230308</t>
+  </si>
+  <si>
+    <t>B230305</t>
+  </si>
+  <si>
+    <t>CL1402F2S</t>
+  </si>
+  <si>
+    <t>材料科学基础（混合式）</t>
+  </si>
+  <si>
+    <t>B240606</t>
+  </si>
+  <si>
+    <t>黄镇东/李子全</t>
+  </si>
+  <si>
+    <t>李平</t>
+  </si>
+  <si>
+    <t>B230603(CW)</t>
+  </si>
+  <si>
+    <t>尹超</t>
+  </si>
+  <si>
+    <t>B240603</t>
+  </si>
+  <si>
+    <t>谢晨</t>
+  </si>
+  <si>
+    <t>马云/魏娟</t>
+  </si>
+  <si>
+    <t>CL1410F2S</t>
+  </si>
+  <si>
+    <t>物理化学（上）(混合式）</t>
+  </si>
+  <si>
+    <t>林秀婧</t>
+  </si>
+  <si>
+    <t>周馨慧</t>
+  </si>
+  <si>
+    <t>韩泽尧</t>
+  </si>
+  <si>
+    <t>B230607</t>
+  </si>
+  <si>
+    <t>B220601(GF)</t>
+  </si>
+  <si>
+    <t>梁铭利</t>
+  </si>
+  <si>
+    <t>CL1411F2S</t>
+  </si>
+  <si>
+    <t>有机化学(下)(混合式)</t>
+  </si>
+  <si>
+    <t>梅群波/许文娟</t>
+  </si>
+  <si>
+    <t>第18周周7(2026-07-05) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>B230601(GF)</t>
+  </si>
+  <si>
+    <t>B230602(GF)</t>
+  </si>
+  <si>
+    <t>B210503(GF)</t>
+  </si>
+  <si>
+    <t>CL1412F2S</t>
+  </si>
+  <si>
+    <t>高分子化学</t>
+  </si>
+  <si>
+    <t>陈润锋</t>
+  </si>
+  <si>
+    <t>徐申</t>
+  </si>
+  <si>
+    <t>CL1415F2S</t>
+  </si>
+  <si>
+    <t>材料力学</t>
+  </si>
+  <si>
+    <t>曹昆</t>
+  </si>
+  <si>
+    <t>第18周周6(2026-07-04) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>CL1421F2S</t>
+  </si>
+  <si>
+    <t>李雯/仪明东</t>
+  </si>
+  <si>
+    <t>李谊</t>
+  </si>
+  <si>
+    <t>仪明东/李雯</t>
+  </si>
+  <si>
+    <t>刘利会/李明光</t>
+  </si>
+  <si>
+    <t>李明光/刘利会</t>
+  </si>
+  <si>
+    <t>CL1422F2S</t>
+  </si>
+  <si>
+    <t>量子力学</t>
+  </si>
+  <si>
+    <t>李兴鳌</t>
+  </si>
+  <si>
+    <t>B230604(CW)</t>
+  </si>
+  <si>
+    <t>CL1423F2S</t>
+  </si>
+  <si>
+    <t>材料分析技术</t>
+  </si>
+  <si>
+    <t>沈清明/李美星</t>
+  </si>
+  <si>
+    <t>第18周周7(2026-07-05) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>曾文进</t>
+  </si>
+  <si>
+    <t>CL1431F2S</t>
+  </si>
+  <si>
+    <t>材料有机化学（混合式）</t>
+  </si>
+  <si>
+    <t>郭珂/张雨霞</t>
+  </si>
+  <si>
+    <t>B230605</t>
+  </si>
+  <si>
+    <t>B220605</t>
+  </si>
+  <si>
+    <t>CL1432F2S</t>
+  </si>
+  <si>
+    <t>电化学原理与应用（双语）</t>
+  </si>
+  <si>
+    <t>李盼/赵进</t>
+  </si>
+  <si>
+    <t>CL1433F2S</t>
+  </si>
+  <si>
+    <t>李慧/赵为为</t>
+  </si>
+  <si>
+    <t>CL1529F2S</t>
+  </si>
+  <si>
+    <t>薄膜物理与技术（混合式）</t>
+  </si>
+  <si>
+    <t>李绍周</t>
+  </si>
+  <si>
+    <t>B220603(CW)</t>
+  </si>
+  <si>
+    <t>CL1612F2S</t>
+  </si>
+  <si>
+    <t>化工原理基础</t>
+  </si>
+  <si>
+    <t>杨文静</t>
+  </si>
+  <si>
+    <t>CL1613F2S</t>
+  </si>
+  <si>
+    <t>聚合物成型工艺与加工基础</t>
+  </si>
+  <si>
+    <t>叶尚辉</t>
+  </si>
+  <si>
+    <t>CL1614F2S</t>
+  </si>
+  <si>
+    <t>功能高分子材料</t>
+  </si>
+  <si>
+    <t>宇文力辉</t>
+  </si>
+  <si>
+    <t>第17周周6(2026-06-27) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>CL1615F2C</t>
+  </si>
+  <si>
+    <t>有机功能材料与器件</t>
+  </si>
+  <si>
+    <t>曹洪涛/凌海峰</t>
+  </si>
+  <si>
+    <t>CL1622F2S</t>
+  </si>
+  <si>
+    <t>材料物理实验</t>
+  </si>
+  <si>
+    <t>黄镇东/李佳慧</t>
+  </si>
+  <si>
+    <t>李佳慧/黄镇东</t>
+  </si>
+  <si>
+    <t>CL1623F2S</t>
+  </si>
+  <si>
+    <t>光电功能材料及应用</t>
+  </si>
+  <si>
+    <t>刘湘梅</t>
+  </si>
+  <si>
+    <t>CL1625F2S</t>
+  </si>
+  <si>
+    <t>平板显示技术</t>
+  </si>
+  <si>
+    <t>牛巧利</t>
+  </si>
+  <si>
+    <t>CL1634F2S</t>
+  </si>
+  <si>
+    <t>CL1626F2S</t>
+  </si>
+  <si>
+    <t>陈淑芬</t>
+  </si>
+  <si>
+    <t>CL1631F2S</t>
+  </si>
+  <si>
+    <t>锂离子电池综合实验</t>
+  </si>
+  <si>
+    <t>张丽/李佳慧/林秀婧</t>
+  </si>
+  <si>
+    <t>第18周周7(2026-07-05) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>林秀婧/李佳慧/张丽</t>
+  </si>
+  <si>
+    <t>李佳慧/林秀婧/张丽</t>
+  </si>
+  <si>
+    <t>CL1632F2S</t>
+  </si>
+  <si>
+    <t>储能材料与器件</t>
+  </si>
+  <si>
+    <t>曹越/李佳慧</t>
+  </si>
+  <si>
+    <t>CL1633F2S</t>
+  </si>
+  <si>
+    <t>材料制备与加工技术</t>
+  </si>
+  <si>
+    <t>吕文珍</t>
+  </si>
+  <si>
+    <t>CL1635F2C</t>
+  </si>
+  <si>
+    <t>锂离子电池制造工艺原理与应用</t>
+  </si>
+  <si>
+    <t>杨方麒/张丽</t>
   </si>
 </sst>
 </file>
@@ -4269,7 +4719,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1553"/>
+  <dimension ref="A1:I1660"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -48425,28 +48875,28 @@
       <c r="A1523" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1523" s="7" t="s">
+      <c r="B1523" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1523" s="7" t="s">
+      <c r="C1523" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="D1523" s="7" t="s">
+      <c r="D1523" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="E1523" s="7" t="s">
+      <c r="E1523" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F1523" s="7" t="s">
+      <c r="F1523" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="G1523" s="7">
+      <c r="G1523" s="6">
         <v>25</v>
       </c>
-      <c r="H1523" s="7" t="s">
+      <c r="H1523" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1523" s="7" t="s">
+      <c r="I1523" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -48454,28 +48904,28 @@
       <c r="A1524" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1524" s="7" t="s">
+      <c r="B1524" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1524" s="7" t="s">
+      <c r="C1524" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="D1524" s="7" t="s">
+      <c r="D1524" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="E1524" s="7" t="s">
+      <c r="E1524" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="F1524" s="7" t="s">
+      <c r="F1524" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="G1524" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1524" s="7" t="s">
+      <c r="G1524" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1524" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1524" s="7" t="s">
+      <c r="I1524" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -48483,28 +48933,28 @@
       <c r="A1525" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1525" s="7" t="s">
+      <c r="B1525" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1525" s="7" t="s">
+      <c r="C1525" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="D1525" s="7" t="s">
+      <c r="D1525" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="E1525" s="7" t="s">
+      <c r="E1525" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F1525" s="7" t="s">
+      <c r="F1525" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="G1525" s="7">
+      <c r="G1525" s="6">
         <v>21</v>
       </c>
-      <c r="H1525" s="7" t="s">
+      <c r="H1525" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="I1525" s="7" t="s">
+      <c r="I1525" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -48512,28 +48962,28 @@
       <c r="A1526" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1526" s="7" t="s">
+      <c r="B1526" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1526" s="7" t="s">
+      <c r="C1526" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1526" s="7" t="s">
+      <c r="D1526" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1526" s="7" t="s">
+      <c r="E1526" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F1526" s="7" t="s">
+      <c r="F1526" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1526" s="7">
+      <c r="G1526" s="6">
         <v>34</v>
       </c>
-      <c r="H1526" s="7" t="s">
+      <c r="H1526" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1526" s="7" t="s">
+      <c r="I1526" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -48541,28 +48991,28 @@
       <c r="A1527" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1527" s="7" t="s">
+      <c r="B1527" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1527" s="7" t="s">
+      <c r="C1527" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1527" s="7" t="s">
+      <c r="D1527" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1527" s="7" t="s">
+      <c r="E1527" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F1527" s="7" t="s">
+      <c r="F1527" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1527" s="7">
+      <c r="G1527" s="6">
         <v>34</v>
       </c>
-      <c r="H1527" s="7" t="s">
+      <c r="H1527" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1527" s="7" t="s">
+      <c r="I1527" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -48570,28 +49020,28 @@
       <c r="A1528" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1528" s="7" t="s">
+      <c r="B1528" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1528" s="7" t="s">
+      <c r="C1528" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1528" s="7" t="s">
+      <c r="D1528" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1528" s="7" t="s">
+      <c r="E1528" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F1528" s="7" t="s">
+      <c r="F1528" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1528" s="7">
+      <c r="G1528" s="6">
         <v>36</v>
       </c>
-      <c r="H1528" s="7" t="s">
+      <c r="H1528" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1528" s="7" t="s">
+      <c r="I1528" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -48599,28 +49049,28 @@
       <c r="A1529" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1529" s="7" t="s">
+      <c r="B1529" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1529" s="7" t="s">
+      <c r="C1529" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1529" s="7" t="s">
+      <c r="D1529" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1529" s="7" t="s">
+      <c r="E1529" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F1529" s="7" t="s">
+      <c r="F1529" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1529" s="7">
+      <c r="G1529" s="6">
         <v>35</v>
       </c>
-      <c r="H1529" s="7" t="s">
+      <c r="H1529" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1529" s="7" t="s">
+      <c r="I1529" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -48628,28 +49078,28 @@
       <c r="A1530" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1530" s="7" t="s">
+      <c r="B1530" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1530" s="7" t="s">
+      <c r="C1530" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1530" s="7" t="s">
+      <c r="D1530" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1530" s="7" t="s">
+      <c r="E1530" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F1530" s="7" t="s">
+      <c r="F1530" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1530" s="7">
+      <c r="G1530" s="6">
         <v>35</v>
       </c>
-      <c r="H1530" s="7" t="s">
+      <c r="H1530" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1530" s="7" t="s">
+      <c r="I1530" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -48657,28 +49107,28 @@
       <c r="A1531" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1531" s="7" t="s">
+      <c r="B1531" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1531" s="7" t="s">
+      <c r="C1531" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1531" s="7" t="s">
+      <c r="D1531" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1531" s="7" t="s">
+      <c r="E1531" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F1531" s="7" t="s">
+      <c r="F1531" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1531" s="7">
+      <c r="G1531" s="6">
         <v>32</v>
       </c>
-      <c r="H1531" s="7" t="s">
+      <c r="H1531" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1531" s="7" t="s">
+      <c r="I1531" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -48686,28 +49136,28 @@
       <c r="A1532" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1532" s="7" t="s">
+      <c r="B1532" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1532" s="7" t="s">
+      <c r="C1532" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1532" s="7" t="s">
+      <c r="D1532" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1532" s="7" t="s">
+      <c r="E1532" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F1532" s="7" t="s">
+      <c r="F1532" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1532" s="7">
+      <c r="G1532" s="6">
         <v>36</v>
       </c>
-      <c r="H1532" s="7" t="s">
+      <c r="H1532" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1532" s="7" t="s">
+      <c r="I1532" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -48715,28 +49165,28 @@
       <c r="A1533" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1533" s="7" t="s">
+      <c r="B1533" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1533" s="7" t="s">
+      <c r="C1533" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1533" s="7" t="s">
+      <c r="D1533" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1533" s="7" t="s">
+      <c r="E1533" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F1533" s="7" t="s">
+      <c r="F1533" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1533" s="7">
+      <c r="G1533" s="6">
         <v>34</v>
       </c>
-      <c r="H1533" s="7" t="s">
+      <c r="H1533" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1533" s="7" t="s">
+      <c r="I1533" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -48744,28 +49194,28 @@
       <c r="A1534" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1534" s="7" t="s">
+      <c r="B1534" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1534" s="7" t="s">
+      <c r="C1534" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1534" s="7" t="s">
+      <c r="D1534" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1534" s="7" t="s">
+      <c r="E1534" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F1534" s="7" t="s">
+      <c r="F1534" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1534" s="7">
+      <c r="G1534" s="6">
         <v>31</v>
       </c>
-      <c r="H1534" s="7" t="s">
+      <c r="H1534" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1534" s="7" t="s">
+      <c r="I1534" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -48773,28 +49223,28 @@
       <c r="A1535" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1535" s="7" t="s">
+      <c r="B1535" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1535" s="7" t="s">
+      <c r="C1535" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1535" s="7" t="s">
+      <c r="D1535" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1535" s="7" t="s">
+      <c r="E1535" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F1535" s="7" t="s">
+      <c r="F1535" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="G1535" s="7">
+      <c r="G1535" s="6">
         <v>34</v>
       </c>
-      <c r="H1535" s="7" t="s">
+      <c r="H1535" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1535" s="7" t="s">
+      <c r="I1535" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -48802,28 +49252,28 @@
       <c r="A1536" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1536" s="7" t="s">
+      <c r="B1536" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1536" s="7" t="s">
+      <c r="C1536" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1536" s="7" t="s">
+      <c r="D1536" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1536" s="7" t="s">
+      <c r="E1536" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F1536" s="7" t="s">
+      <c r="F1536" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="G1536" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1536" s="7" t="s">
+      <c r="G1536" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1536" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1536" s="7" t="s">
+      <c r="I1536" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -48831,28 +49281,28 @@
       <c r="A1537" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1537" s="7" t="s">
+      <c r="B1537" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1537" s="7" t="s">
+      <c r="C1537" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1537" s="7" t="s">
+      <c r="D1537" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1537" s="7" t="s">
+      <c r="E1537" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F1537" s="7" t="s">
+      <c r="F1537" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="G1537" s="7">
+      <c r="G1537" s="6">
         <v>29</v>
       </c>
-      <c r="H1537" s="7" t="s">
+      <c r="H1537" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1537" s="7" t="s">
+      <c r="I1537" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -48860,28 +49310,28 @@
       <c r="A1538" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1538" s="7" t="s">
+      <c r="B1538" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1538" s="7" t="s">
+      <c r="C1538" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1538" s="7" t="s">
+      <c r="D1538" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1538" s="7" t="s">
+      <c r="E1538" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F1538" s="7" t="s">
+      <c r="F1538" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="G1538" s="7">
+      <c r="G1538" s="6">
         <v>33</v>
       </c>
-      <c r="H1538" s="7" t="s">
+      <c r="H1538" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1538" s="7" t="s">
+      <c r="I1538" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -48889,28 +49339,28 @@
       <c r="A1539" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1539" s="7" t="s">
+      <c r="B1539" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1539" s="7" t="s">
+      <c r="C1539" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1539" s="7" t="s">
+      <c r="D1539" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1539" s="7" t="s">
+      <c r="E1539" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="F1539" s="7" t="s">
+      <c r="F1539" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="G1539" s="7">
+      <c r="G1539" s="6">
         <v>2</v>
       </c>
-      <c r="H1539" s="7" t="s">
+      <c r="H1539" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1539" s="7" t="s">
+      <c r="I1539" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -48918,28 +49368,28 @@
       <c r="A1540" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1540" s="7" t="s">
+      <c r="B1540" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1540" s="7" t="s">
+      <c r="C1540" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1540" s="7" t="s">
+      <c r="D1540" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1540" s="7" t="s">
+      <c r="E1540" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F1540" s="7" t="s">
+      <c r="F1540" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="G1540" s="7">
+      <c r="G1540" s="6">
         <v>33</v>
       </c>
-      <c r="H1540" s="7" t="s">
+      <c r="H1540" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1540" s="7" t="s">
+      <c r="I1540" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -48947,28 +49397,28 @@
       <c r="A1541" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1541" s="7" t="s">
+      <c r="B1541" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1541" s="7" t="s">
+      <c r="C1541" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1541" s="7" t="s">
+      <c r="D1541" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1541" s="7" t="s">
+      <c r="E1541" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F1541" s="7" t="s">
+      <c r="F1541" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="G1541" s="7">
+      <c r="G1541" s="6">
         <v>26</v>
       </c>
-      <c r="H1541" s="7" t="s">
+      <c r="H1541" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1541" s="7" t="s">
+      <c r="I1541" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -48976,28 +49426,28 @@
       <c r="A1542" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1542" s="7" t="s">
+      <c r="B1542" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1542" s="7" t="s">
+      <c r="C1542" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1542" s="7" t="s">
+      <c r="D1542" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1542" s="7" t="s">
+      <c r="E1542" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F1542" s="7" t="s">
+      <c r="F1542" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="G1542" s="7">
+      <c r="G1542" s="6">
         <v>31</v>
       </c>
-      <c r="H1542" s="7" t="s">
+      <c r="H1542" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1542" s="7" t="s">
+      <c r="I1542" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -49005,28 +49455,28 @@
       <c r="A1543" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1543" s="7" t="s">
+      <c r="B1543" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1543" s="7" t="s">
+      <c r="C1543" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1543" s="7" t="s">
+      <c r="D1543" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1543" s="7" t="s">
+      <c r="E1543" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F1543" s="7" t="s">
+      <c r="F1543" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="G1543" s="7">
+      <c r="G1543" s="6">
         <v>31</v>
       </c>
-      <c r="H1543" s="7" t="s">
+      <c r="H1543" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1543" s="7" t="s">
+      <c r="I1543" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49034,28 +49484,28 @@
       <c r="A1544" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1544" s="7" t="s">
+      <c r="B1544" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1544" s="7" t="s">
+      <c r="C1544" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1544" s="7" t="s">
+      <c r="D1544" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1544" s="7" t="s">
+      <c r="E1544" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F1544" s="7" t="s">
+      <c r="F1544" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1544" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1544" s="7" t="s">
+      <c r="G1544" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1544" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1544" s="7" t="s">
+      <c r="I1544" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49063,28 +49513,28 @@
       <c r="A1545" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1545" s="7" t="s">
+      <c r="B1545" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1545" s="7" t="s">
+      <c r="C1545" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1545" s="7" t="s">
+      <c r="D1545" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1545" s="7" t="s">
+      <c r="E1545" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F1545" s="7" t="s">
+      <c r="F1545" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1545" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1545" s="7" t="s">
+      <c r="G1545" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1545" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1545" s="7" t="s">
+      <c r="I1545" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49092,28 +49542,28 @@
       <c r="A1546" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1546" s="7" t="s">
+      <c r="B1546" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1546" s="7" t="s">
+      <c r="C1546" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1546" s="7" t="s">
+      <c r="D1546" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="E1546" s="7" t="s">
+      <c r="E1546" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F1546" s="7" t="s">
+      <c r="F1546" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1546" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1546" s="7" t="s">
+      <c r="G1546" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1546" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1546" s="7" t="s">
+      <c r="I1546" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49121,28 +49571,28 @@
       <c r="A1547" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1547" s="7" t="s">
+      <c r="B1547" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1547" s="7" t="s">
+      <c r="C1547" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1547" s="7" t="s">
+      <c r="D1547" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="E1547" s="7" t="s">
+      <c r="E1547" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F1547" s="7" t="s">
+      <c r="F1547" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1547" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1547" s="7" t="s">
+      <c r="G1547" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1547" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1547" s="7" t="s">
+      <c r="I1547" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49150,28 +49600,28 @@
       <c r="A1548" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1548" s="7" t="s">
+      <c r="B1548" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1548" s="7" t="s">
+      <c r="C1548" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1548" s="7" t="s">
+      <c r="D1548" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="E1548" s="7" t="s">
+      <c r="E1548" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F1548" s="7" t="s">
+      <c r="F1548" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1548" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1548" s="7" t="s">
+      <c r="G1548" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1548" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1548" s="7" t="s">
+      <c r="I1548" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49179,28 +49629,28 @@
       <c r="A1549" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1549" s="7" t="s">
+      <c r="B1549" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1549" s="7" t="s">
+      <c r="C1549" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1549" s="7" t="s">
+      <c r="D1549" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1549" s="7" t="s">
+      <c r="E1549" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F1549" s="7" t="s">
+      <c r="F1549" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1549" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1549" s="7" t="s">
+      <c r="G1549" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1549" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1549" s="7" t="s">
+      <c r="I1549" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49208,28 +49658,28 @@
       <c r="A1550" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1550" s="7" t="s">
+      <c r="B1550" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1550" s="7" t="s">
+      <c r="C1550" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1550" s="7" t="s">
+      <c r="D1550" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1550" s="7" t="s">
+      <c r="E1550" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F1550" s="7" t="s">
+      <c r="F1550" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1550" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1550" s="7" t="s">
+      <c r="G1550" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1550" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1550" s="7" t="s">
+      <c r="I1550" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49237,28 +49687,28 @@
       <c r="A1551" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1551" s="7" t="s">
+      <c r="B1551" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1551" s="7" t="s">
+      <c r="C1551" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1551" s="7" t="s">
+      <c r="D1551" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1551" s="7" t="s">
+      <c r="E1551" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F1551" s="7" t="s">
+      <c r="F1551" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1551" s="7">
+      <c r="G1551" s="6">
         <v>36</v>
       </c>
-      <c r="H1551" s="7" t="s">
+      <c r="H1551" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1551" s="7" t="s">
+      <c r="I1551" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49266,28 +49716,28 @@
       <c r="A1552" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1552" s="7" t="s">
+      <c r="B1552" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1552" s="7" t="s">
+      <c r="C1552" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1552" s="7" t="s">
+      <c r="D1552" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1552" s="7" t="s">
+      <c r="E1552" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F1552" s="7" t="s">
+      <c r="F1552" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1552" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1552" s="7" t="s">
+      <c r="G1552" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1552" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1552" s="7" t="s">
+      <c r="I1552" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -49295,29 +49745,3132 @@
       <c r="A1553" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1553" s="7" t="s">
+      <c r="B1553" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C1553" s="7" t="s">
+      <c r="C1553" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="D1553" s="7" t="s">
+      <c r="D1553" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="E1553" s="7" t="s">
+      <c r="E1553" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F1553" s="7" t="s">
+      <c r="F1553" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="G1553" s="7">
-        <v>1</v>
-      </c>
-      <c r="H1553" s="7" t="s">
+      <c r="G1553" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1553" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I1553" s="7" t="s">
+      <c r="I1553" s="6" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:9">
+      <c r="A1554" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1554" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1554" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D1554" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E1554" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1554" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G1554" s="6">
+        <v>19</v>
+      </c>
+      <c r="H1554" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1554" s="6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:9">
+      <c r="A1555" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1555" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1555" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D1555" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E1555" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F1555" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G1555" s="6">
+        <v>17</v>
+      </c>
+      <c r="H1555" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1555" s="6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:9">
+      <c r="A1556" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1556" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1556" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D1556" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E1556" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1556" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G1556" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1556" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I1556" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:9">
+      <c r="A1557" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1557" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1557" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D1557" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E1557" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F1557" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G1557" s="6">
+        <v>30</v>
+      </c>
+      <c r="H1557" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I1557" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:9">
+      <c r="A1558" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1558" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1558" s="6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D1558" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E1558" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1558" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G1558" s="6">
+        <v>17</v>
+      </c>
+      <c r="H1558" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="I1558" s="6" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:9">
+      <c r="A1559" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1559" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1559" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D1559" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E1559" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1559" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G1559" s="6">
+        <v>19</v>
+      </c>
+      <c r="H1559" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="I1559" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:9">
+      <c r="A1560" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1560" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1560" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D1560" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E1560" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F1560" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G1560" s="6">
+        <v>17</v>
+      </c>
+      <c r="H1560" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="I1560" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:9">
+      <c r="A1561" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1561" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1561" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D1561" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E1561" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1561" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G1561" s="6">
+        <v>22</v>
+      </c>
+      <c r="H1561" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I1561" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:9">
+      <c r="A1562" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1562" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1562" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D1562" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E1562" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1562" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G1562" s="6">
+        <v>13</v>
+      </c>
+      <c r="H1562" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1562" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:9">
+      <c r="A1563" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1563" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1563" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D1563" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E1563" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F1563" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G1563" s="6">
+        <v>13</v>
+      </c>
+      <c r="H1563" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1563" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:9">
+      <c r="A1564" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1564" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1564" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D1564" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E1564" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="F1564" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G1564" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1564" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1564" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:9">
+      <c r="A1565" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1565" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1565" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D1565" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E1565" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1565" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G1565" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1565" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1565" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:9">
+      <c r="A1566" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1566" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1566" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D1566" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E1566" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F1566" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G1566" s="6">
+        <v>30</v>
+      </c>
+      <c r="H1566" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1566" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:9">
+      <c r="A1567" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1567" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1567" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D1567" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1567" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1567" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="G1567" s="6">
+        <v>22</v>
+      </c>
+      <c r="H1567" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="I1567" s="6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:9">
+      <c r="A1568" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1568" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1568" s="6" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D1568" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E1568" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1568" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G1568" s="6">
+        <v>22</v>
+      </c>
+      <c r="H1568" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="I1568" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:9">
+      <c r="A1569" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1569" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1569" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D1569" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E1569" s="6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F1569" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G1569" s="6">
+        <v>23</v>
+      </c>
+      <c r="H1569" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I1569" s="6" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:9">
+      <c r="A1570" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1570" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1570" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D1570" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1570" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1570" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1570" s="7">
+        <v>3</v>
+      </c>
+      <c r="H1570" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1570" s="7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:9">
+      <c r="A1571" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1571" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1571" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D1571" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1571" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F1571" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1571" s="7">
+        <v>3</v>
+      </c>
+      <c r="H1571" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1571" s="7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:9">
+      <c r="A1572" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1572" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1572" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D1572" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1572" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F1572" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1572" s="7">
+        <v>6</v>
+      </c>
+      <c r="H1572" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1572" s="7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:9">
+      <c r="A1573" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1573" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1573" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D1573" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1573" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="F1573" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1573" s="7">
+        <v>5</v>
+      </c>
+      <c r="H1573" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1573" s="7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:9">
+      <c r="A1574" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1574" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1574" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D1574" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1574" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F1574" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1574" s="7">
+        <v>2</v>
+      </c>
+      <c r="H1574" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1574" s="7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:9">
+      <c r="A1575" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1575" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1575" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1575" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1575" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1575" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G1575" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1575" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1575" s="7" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:9">
+      <c r="A1576" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1576" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1576" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1576" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1576" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1576" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G1576" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1576" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1576" s="7" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:9">
+      <c r="A1577" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1577" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1577" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1577" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1577" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1577" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G1577" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1577" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1577" s="7" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:9">
+      <c r="A1578" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1578" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1578" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1578" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1578" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F1578" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G1578" s="7">
+        <v>26</v>
+      </c>
+      <c r="H1578" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1578" s="7" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:9">
+      <c r="A1579" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1579" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1579" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1579" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1579" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F1579" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G1579" s="7">
+        <v>24</v>
+      </c>
+      <c r="H1579" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1579" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:9">
+      <c r="A1580" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1580" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1580" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1580" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1580" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1580" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G1580" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1580" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1580" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:9">
+      <c r="A1581" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1581" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1581" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1581" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1581" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1581" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G1581" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1581" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1581" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:9">
+      <c r="A1582" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1582" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1582" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1582" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1582" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1582" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G1582" s="7">
+        <v>29</v>
+      </c>
+      <c r="H1582" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1582" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:9">
+      <c r="A1583" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1583" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1583" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1583" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1583" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1583" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G1583" s="7">
+        <v>2</v>
+      </c>
+      <c r="H1583" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1583" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:9">
+      <c r="A1584" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1584" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1584" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1584" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1584" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1584" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G1584" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1584" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1584" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:9">
+      <c r="A1585" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1585" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1585" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1585" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1585" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1585" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G1585" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1585" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1585" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:9">
+      <c r="A1586" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1586" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1586" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1586" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1586" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1586" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G1586" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1586" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1586" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:9">
+      <c r="A1587" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1587" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1587" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1587" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1587" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F1587" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G1587" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1587" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1587" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:9">
+      <c r="A1588" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1588" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1588" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1588" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1588" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1588" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G1588" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1588" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1588" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:9">
+      <c r="A1589" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1589" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1589" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1589" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1589" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1589" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1589" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1589" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1589" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:9">
+      <c r="A1590" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1590" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1590" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1590" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1590" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1590" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1590" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1590" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1590" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:9">
+      <c r="A1591" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1591" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1591" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1591" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1591" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1591" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1591" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1591" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1591" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:9">
+      <c r="A1592" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1592" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1592" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1592" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1592" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1592" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1592" s="7">
+        <v>5</v>
+      </c>
+      <c r="H1592" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1592" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:9">
+      <c r="A1593" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1593" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1593" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1593" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1593" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1593" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1593" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1593" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1593" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:9">
+      <c r="A1594" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1594" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1594" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D1594" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1594" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F1594" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1594" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1594" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1594" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:9">
+      <c r="A1595" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1595" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1595" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D1595" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E1595" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1595" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G1595" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1595" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1595" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:9">
+      <c r="A1596" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1596" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1596" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D1596" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E1596" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1596" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G1596" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1596" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1596" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:9">
+      <c r="A1597" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1597" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1597" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D1597" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1597" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1597" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1597" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1597" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1597" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:9">
+      <c r="A1598" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1598" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1598" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D1598" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1598" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F1598" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G1598" s="7">
+        <v>24</v>
+      </c>
+      <c r="H1598" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1598" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:9">
+      <c r="A1599" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1599" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1599" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D1599" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1599" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1599" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G1599" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1599" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1599" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:9">
+      <c r="A1600" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1600" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1600" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D1600" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1600" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F1600" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G1600" s="7">
+        <v>26</v>
+      </c>
+      <c r="H1600" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1600" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:9">
+      <c r="A1601" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1601" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1601" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D1601" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1601" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="F1601" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G1601" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1601" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1601" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:9">
+      <c r="A1602" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1602" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1602" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D1602" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1602" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1602" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G1602" s="7">
+        <v>28</v>
+      </c>
+      <c r="H1602" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1602" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:9">
+      <c r="A1603" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1603" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1603" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D1603" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1603" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1603" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1603" s="7">
+        <v>2</v>
+      </c>
+      <c r="H1603" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1603" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:9">
+      <c r="A1604" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1604" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1604" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D1604" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1604" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1604" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1604" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1604" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1604" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:9">
+      <c r="A1605" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1605" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1605" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D1605" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1605" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F1605" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1605" s="7">
+        <v>24</v>
+      </c>
+      <c r="H1605" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1605" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:9">
+      <c r="A1606" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1606" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1606" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D1606" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1606" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F1606" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1606" s="7">
+        <v>26</v>
+      </c>
+      <c r="H1606" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1606" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:9">
+      <c r="A1607" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1607" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1607" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D1607" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E1607" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F1607" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G1607" s="7">
+        <v>24</v>
+      </c>
+      <c r="H1607" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1607" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:9">
+      <c r="A1608" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1608" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1608" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D1608" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E1608" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F1608" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G1608" s="7">
+        <v>26</v>
+      </c>
+      <c r="H1608" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1608" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:9">
+      <c r="A1609" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1609" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1609" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1609" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1609" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1609" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1609" s="7">
+        <v>29</v>
+      </c>
+      <c r="H1609" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1609" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:9">
+      <c r="A1610" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1610" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1610" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1610" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1610" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1610" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1610" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1610" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1610" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:9">
+      <c r="A1611" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1611" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1611" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1611" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1611" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1611" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1611" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1611" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1611" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:9">
+      <c r="A1612" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1612" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1612" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1612" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1612" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1612" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1612" s="7">
+        <v>2</v>
+      </c>
+      <c r="H1612" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1612" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:9">
+      <c r="A1613" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1613" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1613" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1613" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1613" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1613" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1613" s="7">
+        <v>3</v>
+      </c>
+      <c r="H1613" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1613" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:9">
+      <c r="A1614" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1614" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1614" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1614" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1614" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F1614" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1614" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1614" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1614" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:9">
+      <c r="A1615" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1615" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1615" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D1615" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1615" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F1615" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1615" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1615" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1615" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:9">
+      <c r="A1616" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1616" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1616" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D1616" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1616" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1616" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G1616" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1616" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1616" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:9">
+      <c r="A1617" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1617" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1617" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D1617" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1617" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1617" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G1617" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1617" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1617" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:9">
+      <c r="A1618" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1618" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1618" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D1618" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1618" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1618" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G1618" s="7">
+        <v>29</v>
+      </c>
+      <c r="H1618" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1618" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:9">
+      <c r="A1619" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1619" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1619" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D1619" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E1619" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1619" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G1619" s="7">
+        <v>33</v>
+      </c>
+      <c r="H1619" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1619" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:9">
+      <c r="A1620" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1620" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1620" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D1620" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E1620" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F1620" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G1620" s="7">
+        <v>29</v>
+      </c>
+      <c r="H1620" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1620" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:9">
+      <c r="A1621" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1621" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1621" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D1621" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1621" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1621" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1621" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1621" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1621" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:9">
+      <c r="A1622" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1622" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1622" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D1622" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1622" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1622" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1622" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1622" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1622" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:9">
+      <c r="A1623" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1623" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1623" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D1623" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1623" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F1623" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1623" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1623" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1623" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:9">
+      <c r="A1624" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1624" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1624" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D1624" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1624" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1624" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1624" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1624" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1624" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:9">
+      <c r="A1625" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1625" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1625" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D1625" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1625" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1625" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G1625" s="7">
+        <v>12</v>
+      </c>
+      <c r="H1625" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1625" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:9">
+      <c r="A1626" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1626" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1626" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D1626" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1626" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1626" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G1626" s="7">
+        <v>7</v>
+      </c>
+      <c r="H1626" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1626" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:9">
+      <c r="A1627" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1627" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1627" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D1627" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1627" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1627" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G1627" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1627" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1627" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:9">
+      <c r="A1628" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1628" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1628" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D1628" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1628" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1628" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G1628" s="7">
+        <v>22</v>
+      </c>
+      <c r="H1628" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1628" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:9">
+      <c r="A1629" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1629" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1629" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D1629" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1629" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1629" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G1629" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1629" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1629" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:9">
+      <c r="A1630" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1630" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1630" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D1630" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1630" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1630" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G1630" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1630" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1630" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:9">
+      <c r="A1631" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1631" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1631" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D1631" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E1631" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1631" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G1631" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1631" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I1631" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:9">
+      <c r="A1632" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1632" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1632" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D1632" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E1632" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1632" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G1632" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1632" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I1632" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:9">
+      <c r="A1633" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1633" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1633" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D1633" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E1633" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1633" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G1633" s="7">
+        <v>24</v>
+      </c>
+      <c r="H1633" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1633" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:9">
+      <c r="A1634" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1634" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1634" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D1634" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E1634" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1634" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G1634" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1634" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1634" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:9">
+      <c r="A1635" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1635" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1635" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D1635" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E1635" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1635" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G1635" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1635" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I1635" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:9">
+      <c r="A1636" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1636" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1636" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D1636" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E1636" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1636" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G1636" s="7">
+        <v>22</v>
+      </c>
+      <c r="H1636" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I1636" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:9">
+      <c r="A1637" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1637" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1637" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D1637" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E1637" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1637" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G1637" s="7">
+        <v>21</v>
+      </c>
+      <c r="H1637" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1637" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:9">
+      <c r="A1638" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1638" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1638" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D1638" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E1638" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1638" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G1638" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1638" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1638" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:9">
+      <c r="A1639" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1639" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1639" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D1639" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E1639" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1639" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G1639" s="7">
+        <v>22</v>
+      </c>
+      <c r="H1639" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1639" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:9">
+      <c r="A1640" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1640" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1640" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D1640" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E1640" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1640" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G1640" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1640" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1640" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:9">
+      <c r="A1641" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1641" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1641" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1641" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1641" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1641" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1641" s="7">
+        <v>12</v>
+      </c>
+      <c r="H1641" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1641" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:9">
+      <c r="A1642" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1642" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1642" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1642" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1642" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1642" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1642" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1642" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1642" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:9">
+      <c r="A1643" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1643" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1643" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1643" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1643" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1643" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1643" s="7">
+        <v>13</v>
+      </c>
+      <c r="H1643" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1643" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:9">
+      <c r="A1644" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1644" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1644" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1644" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1644" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F1644" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1644" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1644" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1644" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:9">
+      <c r="A1645" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1645" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1645" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D1645" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1645" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1645" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G1645" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1645" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1645" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:9">
+      <c r="A1646" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1646" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1646" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D1646" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1646" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F1646" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G1646" s="7">
+        <v>19</v>
+      </c>
+      <c r="H1646" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="I1646" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:9">
+      <c r="A1647" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1647" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1647" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D1647" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1647" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1647" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G1647" s="7">
+        <v>16</v>
+      </c>
+      <c r="H1647" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I1647" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:9">
+      <c r="A1648" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1648" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1648" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D1648" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1648" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1648" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G1648" s="7">
+        <v>17</v>
+      </c>
+      <c r="H1648" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I1648" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:9">
+      <c r="A1649" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1649" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1649" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D1649" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1649" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1649" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G1649" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1649" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I1649" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:9">
+      <c r="A1650" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1650" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1650" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D1650" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E1650" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1650" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G1650" s="7">
+        <v>16</v>
+      </c>
+      <c r="H1650" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1650" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:9">
+      <c r="A1651" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1651" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1651" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D1651" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E1651" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1651" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G1651" s="7">
+        <v>17</v>
+      </c>
+      <c r="H1651" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1651" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:9">
+      <c r="A1652" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1652" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1652" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D1652" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E1652" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1652" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G1652" s="7">
+        <v>23</v>
+      </c>
+      <c r="H1652" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I1652" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:9">
+      <c r="A1653" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1653" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1653" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1653" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1653" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1653" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G1653" s="7">
+        <v>17</v>
+      </c>
+      <c r="H1653" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1653" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:9">
+      <c r="A1654" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1654" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1654" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1654" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1654" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1654" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G1654" s="7">
+        <v>16</v>
+      </c>
+      <c r="H1654" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1654" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:9">
+      <c r="A1655" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1655" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1655" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1655" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1655" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1655" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G1655" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1655" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1655" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:9">
+      <c r="A1656" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1656" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1656" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1656" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1656" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F1656" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G1656" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1656" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="I1656" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:9">
+      <c r="A1657" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1657" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1657" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D1657" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1657" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1657" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G1657" s="7">
+        <v>25</v>
+      </c>
+      <c r="H1657" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="I1657" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:9">
+      <c r="A1658" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1658" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1658" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D1658" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1658" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F1658" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G1658" s="7">
+        <v>17</v>
+      </c>
+      <c r="H1658" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="I1658" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:9">
+      <c r="A1659" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1659" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1659" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D1659" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1659" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F1659" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G1659" s="7">
+        <v>15</v>
+      </c>
+      <c r="H1659" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="I1659" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:9">
+      <c r="A1660" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1660" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1660" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D1660" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1660" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F1660" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G1660" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1660" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="I1660" s="7" t="s">
+        <v>765</v>
       </c>
     </row>
   </sheetData>
